--- a/research/traditional_assets/database/data/bulgaria/bulgaria_power.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_power.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07459822422242117</v>
+        <v>0.07456412599819875</v>
       </c>
       <c r="C2">
-        <v>198.4723405919734</v>
+        <v>196.9958845420098</v>
       </c>
       <c r="D2">
-        <v>198.3283405919734</v>
+        <v>198.5448845420098</v>
       </c>
       <c r="E2">
-        <v>-51.9</v>
+        <v>-50.207</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.693</v>
       </c>
       <c r="G2">
         <v>0.144</v>
@@ -1445,28 +1445,28 @@
         <v>11.07</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08515789999999999</v>
       </c>
       <c r="N2">
-        <v>11.07</v>
+        <v>10.9848421</v>
       </c>
       <c r="O2">
-        <v>1.107</v>
+        <v>1.09848421</v>
       </c>
       <c r="P2">
-        <v>9.963000000000001</v>
+        <v>9.886357889999999</v>
       </c>
       <c r="Q2">
-        <v>18.893</v>
+        <v>18.81635789</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07459822422242117</v>
+        <v>0.07486002626080682</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4495493640588392</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>129.9938114960562</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07456412599819875</v>
+        <v>0.07453002777397633</v>
       </c>
       <c r="C3">
-        <v>196.9958845420098</v>
+        <v>195.519901874077</v>
       </c>
       <c r="D3">
-        <v>198.5448845420098</v>
+        <v>198.761901874077</v>
       </c>
       <c r="E3">
-        <v>-50.207</v>
+        <v>-48.514</v>
       </c>
       <c r="F3">
-        <v>1.693</v>
+        <v>3.386</v>
       </c>
       <c r="G3">
         <v>0.144</v>
@@ -1527,28 +1527,28 @@
         <v>11.07</v>
       </c>
       <c r="M3">
-        <v>0.08515789999999999</v>
+        <v>0.1703158</v>
       </c>
       <c r="N3">
-        <v>10.9848421</v>
+        <v>10.8996842</v>
       </c>
       <c r="O3">
-        <v>1.09848421</v>
+        <v>1.08996842</v>
       </c>
       <c r="P3">
-        <v>9.886357889999999</v>
+        <v>9.809715780000001</v>
       </c>
       <c r="Q3">
-        <v>18.81635789</v>
+        <v>18.73971578</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07486002626080682</v>
+        <v>0.07512717119793502</v>
       </c>
       <c r="T3">
-        <v>0.4495493640588392</v>
+        <v>0.4536820112739416</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>129.9938114960562</v>
+        <v>64.99690574802808</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07453002777397633</v>
+        <v>0.0744959295497539</v>
       </c>
       <c r="C4">
-        <v>195.519901874077</v>
+        <v>194.0443941421487</v>
       </c>
       <c r="D4">
-        <v>198.761901874077</v>
+        <v>198.9793941421487</v>
       </c>
       <c r="E4">
-        <v>-48.514</v>
+        <v>-46.821</v>
       </c>
       <c r="F4">
-        <v>3.386</v>
+        <v>5.079</v>
       </c>
       <c r="G4">
         <v>0.144</v>
@@ -1609,28 +1609,28 @@
         <v>11.07</v>
       </c>
       <c r="M4">
-        <v>0.1703158</v>
+        <v>0.2554737</v>
       </c>
       <c r="N4">
-        <v>10.8996842</v>
+        <v>10.8145263</v>
       </c>
       <c r="O4">
-        <v>1.08996842</v>
+        <v>1.08145263</v>
       </c>
       <c r="P4">
-        <v>9.809715780000001</v>
+        <v>9.733073670000001</v>
       </c>
       <c r="Q4">
-        <v>18.73971578</v>
+        <v>18.66307367</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07512717119793502</v>
+        <v>0.0753998242780968</v>
       </c>
       <c r="T4">
-        <v>0.4536820112739416</v>
+        <v>0.4578998677099739</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.99690574802808</v>
+        <v>43.33127049868539</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0744959295497539</v>
+        <v>0.07446183132553148</v>
       </c>
       <c r="C5">
-        <v>194.0443941421487</v>
+        <v>192.5693629070077</v>
       </c>
       <c r="D5">
-        <v>198.9793941421487</v>
+        <v>199.1973629070077</v>
       </c>
       <c r="E5">
-        <v>-46.821</v>
+        <v>-45.128</v>
       </c>
       <c r="F5">
-        <v>5.079</v>
+        <v>6.772</v>
       </c>
       <c r="G5">
         <v>0.144</v>
@@ -1691,28 +1691,28 @@
         <v>11.07</v>
       </c>
       <c r="M5">
-        <v>0.2554737</v>
+        <v>0.3406316</v>
       </c>
       <c r="N5">
-        <v>10.8145263</v>
+        <v>10.7293684</v>
       </c>
       <c r="O5">
-        <v>1.08145263</v>
+        <v>1.07293684</v>
       </c>
       <c r="P5">
-        <v>9.733073670000001</v>
+        <v>9.65643156</v>
       </c>
       <c r="Q5">
-        <v>18.66307367</v>
+        <v>18.58643156</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0753998242780968</v>
+        <v>0.07567815763076197</v>
       </c>
       <c r="T5">
-        <v>0.4578998677099739</v>
+        <v>0.4622055961550904</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.33127049868539</v>
+        <v>32.49845287401403</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07446183132553148</v>
+        <v>0.07442773310130905</v>
       </c>
       <c r="C6">
-        <v>192.5693629070077</v>
+        <v>191.0948097362837</v>
       </c>
       <c r="D6">
-        <v>199.1973629070077</v>
+        <v>199.4158097362837</v>
       </c>
       <c r="E6">
-        <v>-45.128</v>
+        <v>-43.435</v>
       </c>
       <c r="F6">
-        <v>6.772</v>
+        <v>8.465000000000002</v>
       </c>
       <c r="G6">
         <v>0.144</v>
@@ -1773,28 +1773,28 @@
         <v>11.07</v>
       </c>
       <c r="M6">
-        <v>0.3406316</v>
+        <v>0.4257895</v>
       </c>
       <c r="N6">
-        <v>10.7293684</v>
+        <v>10.6442105</v>
       </c>
       <c r="O6">
-        <v>1.07293684</v>
+        <v>1.06442105</v>
       </c>
       <c r="P6">
-        <v>9.65643156</v>
+        <v>9.57978945</v>
       </c>
       <c r="Q6">
-        <v>18.58643156</v>
+        <v>18.50978945</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07567815763076197</v>
+        <v>0.07596235063295691</v>
       </c>
       <c r="T6">
-        <v>0.4622055961550904</v>
+        <v>0.4666019715148407</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.49845287401403</v>
+        <v>25.99876229921123</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07442773310130905</v>
+        <v>0.07439363487708664</v>
       </c>
       <c r="C7">
-        <v>191.0948097362837</v>
+        <v>189.6207362044898</v>
       </c>
       <c r="D7">
-        <v>199.4158097362837</v>
+        <v>199.6347362044898</v>
       </c>
       <c r="E7">
-        <v>-43.435</v>
+        <v>-41.742</v>
       </c>
       <c r="F7">
-        <v>8.465000000000002</v>
+        <v>10.158</v>
       </c>
       <c r="G7">
         <v>0.144</v>
@@ -1855,28 +1855,28 @@
         <v>11.07</v>
       </c>
       <c r="M7">
-        <v>0.4257895</v>
+        <v>0.5109474000000001</v>
       </c>
       <c r="N7">
-        <v>10.6442105</v>
+        <v>10.5590526</v>
       </c>
       <c r="O7">
-        <v>1.06442105</v>
+        <v>1.05590526</v>
       </c>
       <c r="P7">
-        <v>9.57978945</v>
+        <v>9.503147340000002</v>
       </c>
       <c r="Q7">
-        <v>18.50978945</v>
+        <v>18.43314734</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07596235063295691</v>
+        <v>0.07625259029477302</v>
       </c>
       <c r="T7">
-        <v>0.4666019715148407</v>
+        <v>0.4710918867758624</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.99876229921123</v>
+        <v>21.66563524934269</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07439363487708664</v>
+        <v>0.07435953665286422</v>
       </c>
       <c r="C8">
-        <v>189.6207362044898</v>
+        <v>188.1471438930613</v>
       </c>
       <c r="D8">
-        <v>199.6347362044898</v>
+        <v>199.8541438930613</v>
       </c>
       <c r="E8">
-        <v>-41.742</v>
+        <v>-40.049</v>
       </c>
       <c r="F8">
-        <v>10.158</v>
+        <v>11.851</v>
       </c>
       <c r="G8">
         <v>0.144</v>
@@ -1937,28 +1937,28 @@
         <v>11.07</v>
       </c>
       <c r="M8">
-        <v>0.5109473999999999</v>
+        <v>0.5961052999999999</v>
       </c>
       <c r="N8">
-        <v>10.5590526</v>
+        <v>10.4738947</v>
       </c>
       <c r="O8">
-        <v>1.05590526</v>
+        <v>1.04738947</v>
       </c>
       <c r="P8">
-        <v>9.503147340000002</v>
+        <v>9.42650523</v>
       </c>
       <c r="Q8">
-        <v>18.43314734</v>
+        <v>18.35650523</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07625259029477302</v>
+        <v>0.07654907166974648</v>
       </c>
       <c r="T8">
-        <v>0.4710918867758624</v>
+        <v>0.4756783593543253</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.6656352493427</v>
+        <v>18.5705444994366</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07435953665286422</v>
+        <v>0.07432543842864181</v>
       </c>
       <c r="C9">
-        <v>188.1471438930613</v>
+        <v>186.6740343903934</v>
       </c>
       <c r="D9">
-        <v>199.8541438930613</v>
+        <v>200.0740343903934</v>
       </c>
       <c r="E9">
-        <v>-40.04899999999999</v>
+        <v>-38.35599999999999</v>
       </c>
       <c r="F9">
-        <v>11.851</v>
+        <v>13.544</v>
       </c>
       <c r="G9">
         <v>0.144</v>
@@ -2019,28 +2019,28 @@
         <v>11.07</v>
       </c>
       <c r="M9">
-        <v>0.5961053000000001</v>
+        <v>0.6812632</v>
       </c>
       <c r="N9">
-        <v>10.4738947</v>
+        <v>10.3887368</v>
       </c>
       <c r="O9">
-        <v>1.04738947</v>
+        <v>1.03887368</v>
       </c>
       <c r="P9">
-        <v>9.42650523</v>
+        <v>9.34986312</v>
       </c>
       <c r="Q9">
-        <v>18.35650523</v>
+        <v>18.27986312</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07654907166974648</v>
+        <v>0.07685199829200196</v>
       </c>
       <c r="T9">
-        <v>0.4756783593543255</v>
+        <v>0.4803645378584072</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.57054449943659</v>
+        <v>16.24922643700702</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07432543842864181</v>
+        <v>0.07429134020441938</v>
       </c>
       <c r="C10">
-        <v>186.6740343903934</v>
+        <v>185.2014092918797</v>
       </c>
       <c r="D10">
-        <v>200.0740343903934</v>
+        <v>200.2944092918797</v>
       </c>
       <c r="E10">
-        <v>-38.35599999999999</v>
+        <v>-36.663</v>
       </c>
       <c r="F10">
-        <v>13.544</v>
+        <v>15.237</v>
       </c>
       <c r="G10">
         <v>0.144</v>
@@ -2101,28 +2101,28 @@
         <v>11.07</v>
       </c>
       <c r="M10">
-        <v>0.6812632</v>
+        <v>0.7664211</v>
       </c>
       <c r="N10">
-        <v>10.3887368</v>
+        <v>10.3035789</v>
       </c>
       <c r="O10">
-        <v>1.03887368</v>
+        <v>1.03035789</v>
       </c>
       <c r="P10">
-        <v>9.34986312</v>
+        <v>9.27322101</v>
       </c>
       <c r="Q10">
-        <v>18.27986312</v>
+        <v>18.20322101</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07685199829200196</v>
+        <v>0.07716158264221909</v>
       </c>
       <c r="T10">
-        <v>0.4803645378584072</v>
+        <v>0.4851537092966445</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.24922643700702</v>
+        <v>14.44375683289513</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07429134020441938</v>
+        <v>0.07425724198019697</v>
       </c>
       <c r="C11">
-        <v>185.2014092918797</v>
+        <v>183.7292701999502</v>
       </c>
       <c r="D11">
-        <v>200.2944092918797</v>
+        <v>200.5152701999502</v>
       </c>
       <c r="E11">
-        <v>-36.663</v>
+        <v>-34.97</v>
       </c>
       <c r="F11">
-        <v>15.237</v>
+        <v>16.93</v>
       </c>
       <c r="G11">
         <v>0.144</v>
@@ -2183,28 +2183,28 @@
         <v>11.07</v>
       </c>
       <c r="M11">
-        <v>0.7664211</v>
+        <v>0.851579</v>
       </c>
       <c r="N11">
-        <v>10.3035789</v>
+        <v>10.218421</v>
       </c>
       <c r="O11">
-        <v>1.03035789</v>
+        <v>1.0218421</v>
       </c>
       <c r="P11">
-        <v>9.27322101</v>
+        <v>9.1965789</v>
       </c>
       <c r="Q11">
-        <v>18.20322101</v>
+        <v>18.1265789</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07716158264221909</v>
+        <v>0.07747804664466329</v>
       </c>
       <c r="T11">
-        <v>0.4851537092966445</v>
+        <v>0.4900493067668428</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.44375683289513</v>
+        <v>12.99938114960562</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07425724198019697</v>
+        <v>0.07437164375597452</v>
       </c>
       <c r="C12">
-        <v>183.7292701999502</v>
+        <v>181.297184594058</v>
       </c>
       <c r="D12">
-        <v>200.5152701999502</v>
+        <v>199.776184594058</v>
       </c>
       <c r="E12">
-        <v>-34.97</v>
+        <v>-33.277</v>
       </c>
       <c r="F12">
-        <v>16.93</v>
+        <v>18.623</v>
       </c>
       <c r="G12">
         <v>0.144</v>
@@ -2265,45 +2265,45 @@
         <v>11.07</v>
       </c>
       <c r="M12">
-        <v>0.8515790000000001</v>
+        <v>0.9646714000000001</v>
       </c>
       <c r="N12">
-        <v>10.218421</v>
+        <v>10.1053286</v>
       </c>
       <c r="O12">
-        <v>1.0218421</v>
+        <v>1.01053286</v>
       </c>
       <c r="P12">
-        <v>9.196578899999999</v>
+        <v>9.09479574</v>
       </c>
       <c r="Q12">
-        <v>18.1265789</v>
+        <v>18.02479574</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07747804664466329</v>
+        <v>0.07780162219772419</v>
       </c>
       <c r="T12">
-        <v>0.4900493067668428</v>
+        <v>0.4950549176633375</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>12.99938114960561</v>
+        <v>11.47541017594178</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07437164375597452</v>
+        <v>0.07435104553175212</v>
       </c>
       <c r="C13">
-        <v>181.297184594058</v>
+        <v>179.7368556974969</v>
       </c>
       <c r="D13">
-        <v>199.776184594058</v>
+        <v>199.9088556974969</v>
       </c>
       <c r="E13">
-        <v>-33.277</v>
+        <v>-31.584</v>
       </c>
       <c r="F13">
-        <v>18.623</v>
+        <v>20.316</v>
       </c>
       <c r="G13">
         <v>0.144</v>
@@ -2347,28 +2347,28 @@
         <v>11.07</v>
       </c>
       <c r="M13">
-        <v>0.9646714000000001</v>
+        <v>1.0523688</v>
       </c>
       <c r="N13">
-        <v>10.1053286</v>
+        <v>10.0176312</v>
       </c>
       <c r="O13">
-        <v>1.01053286</v>
+        <v>1.00176312</v>
       </c>
       <c r="P13">
-        <v>9.09479574</v>
+        <v>9.015868080000001</v>
       </c>
       <c r="Q13">
-        <v>18.02479574</v>
+        <v>17.94586808</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07780162219772419</v>
+        <v>0.07813255174062742</v>
       </c>
       <c r="T13">
-        <v>0.4950549176633375</v>
+        <v>0.5001742924438437</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.47541017594178</v>
+        <v>10.5191259946133</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07435104553175212</v>
+        <v>0.07452934730752969</v>
       </c>
       <c r="C14">
-        <v>179.7368556974969</v>
+        <v>176.9012375148123</v>
       </c>
       <c r="D14">
-        <v>199.9088556974969</v>
+        <v>198.7662375148123</v>
       </c>
       <c r="E14">
-        <v>-31.584</v>
+        <v>-29.89099999999999</v>
       </c>
       <c r="F14">
-        <v>20.316</v>
+        <v>22.009</v>
       </c>
       <c r="G14">
         <v>0.144</v>
@@ -2429,45 +2429,45 @@
         <v>11.07</v>
       </c>
       <c r="M14">
-        <v>1.0523688</v>
+        <v>1.1774815</v>
       </c>
       <c r="N14">
-        <v>10.0176312</v>
+        <v>9.8925185</v>
       </c>
       <c r="O14">
-        <v>1.00176312</v>
+        <v>0.98925185</v>
       </c>
       <c r="P14">
-        <v>9.015868080000001</v>
+        <v>8.903266649999999</v>
       </c>
       <c r="Q14">
-        <v>17.94586808</v>
+        <v>17.83326665</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07813255174062742</v>
+        <v>0.07847108885922953</v>
       </c>
       <c r="T14">
-        <v>0.5001742924438437</v>
+        <v>0.5054113540009131</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.5191259946133</v>
+        <v>9.401421593460277</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07452934730752969</v>
+        <v>0.07452404908330726</v>
       </c>
       <c r="C15">
-        <v>176.9012375148123</v>
+        <v>175.2420020011636</v>
       </c>
       <c r="D15">
-        <v>198.7662375148123</v>
+        <v>198.8000020011636</v>
       </c>
       <c r="E15">
-        <v>-29.89099999999999</v>
+        <v>-28.19799999999999</v>
       </c>
       <c r="F15">
-        <v>22.009</v>
+        <v>23.70200000000001</v>
       </c>
       <c r="G15">
         <v>0.144</v>
@@ -2511,28 +2511,28 @@
         <v>11.07</v>
       </c>
       <c r="M15">
-        <v>1.1774815</v>
+        <v>1.268057</v>
       </c>
       <c r="N15">
-        <v>9.8925185</v>
+        <v>9.801943</v>
       </c>
       <c r="O15">
-        <v>0.98925185</v>
+        <v>0.9801943</v>
       </c>
       <c r="P15">
-        <v>8.903266649999999</v>
+        <v>8.821748700000001</v>
       </c>
       <c r="Q15">
-        <v>17.83326665</v>
+        <v>17.7517487</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07847108885922953</v>
+        <v>0.07881749893407822</v>
       </c>
       <c r="T15">
-        <v>0.5054113540009131</v>
+        <v>0.5107702076872167</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.401421593460277</v>
+        <v>8.729891479641687</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07452404908330726</v>
+        <v>0.07451875085908485</v>
       </c>
       <c r="C16">
-        <v>175.2420020011636</v>
+        <v>173.5827779606325</v>
       </c>
       <c r="D16">
-        <v>198.8000020011636</v>
+        <v>198.8337779606325</v>
       </c>
       <c r="E16">
-        <v>-28.19799999999999</v>
+        <v>-26.50499999999999</v>
       </c>
       <c r="F16">
-        <v>23.70200000000001</v>
+        <v>25.39500000000001</v>
       </c>
       <c r="G16">
         <v>0.144</v>
@@ -2593,28 +2593,28 @@
         <v>11.07</v>
       </c>
       <c r="M16">
-        <v>1.268057</v>
+        <v>1.3586325</v>
       </c>
       <c r="N16">
-        <v>9.801943</v>
+        <v>9.7113675</v>
       </c>
       <c r="O16">
-        <v>0.9801943</v>
+        <v>0.97113675</v>
       </c>
       <c r="P16">
-        <v>8.821748700000001</v>
+        <v>8.74023075</v>
       </c>
       <c r="Q16">
-        <v>17.7517487</v>
+        <v>17.67023075</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07881749893407822</v>
+        <v>0.07917205983421748</v>
       </c>
       <c r="T16">
-        <v>0.5107702076872167</v>
+        <v>0.5162551520484921</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.729891479641687</v>
+        <v>8.147898714332239</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07451875085908485</v>
+        <v>0.07451345263486243</v>
       </c>
       <c r="C17">
-        <v>173.5827779606325</v>
+        <v>171.9235653990682</v>
       </c>
       <c r="D17">
-        <v>198.8337779606325</v>
+        <v>198.8675653990682</v>
       </c>
       <c r="E17">
-        <v>-26.505</v>
+        <v>-24.812</v>
       </c>
       <c r="F17">
-        <v>25.395</v>
+        <v>27.088</v>
       </c>
       <c r="G17">
         <v>0.144</v>
@@ -2675,28 +2675,28 @@
         <v>11.07</v>
       </c>
       <c r="M17">
-        <v>1.3586325</v>
+        <v>1.449208</v>
       </c>
       <c r="N17">
-        <v>9.7113675</v>
+        <v>9.620792</v>
       </c>
       <c r="O17">
-        <v>0.97113675</v>
+        <v>0.9620792</v>
       </c>
       <c r="P17">
-        <v>8.74023075</v>
+        <v>8.6587128</v>
       </c>
       <c r="Q17">
-        <v>17.67023075</v>
+        <v>17.5887128</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07917205983421748</v>
+        <v>0.07953506266055052</v>
       </c>
       <c r="T17">
-        <v>0.5162551520484921</v>
+        <v>0.5218706903231313</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.147898714332243</v>
+        <v>7.638655044686477</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07451345263486243</v>
+        <v>0.07463055441064001</v>
       </c>
       <c r="C18">
-        <v>171.9235653990682</v>
+        <v>169.4864605151906</v>
       </c>
       <c r="D18">
-        <v>198.8675653990682</v>
+        <v>198.1234605151906</v>
       </c>
       <c r="E18">
-        <v>-24.812</v>
+        <v>-23.119</v>
       </c>
       <c r="F18">
-        <v>27.088</v>
+        <v>28.781</v>
       </c>
       <c r="G18">
         <v>0.144</v>
@@ -2757,45 +2757,45 @@
         <v>11.07</v>
       </c>
       <c r="M18">
-        <v>1.449208</v>
+        <v>1.5628083</v>
       </c>
       <c r="N18">
-        <v>9.620792</v>
+        <v>9.5071917</v>
       </c>
       <c r="O18">
-        <v>0.9620792</v>
+        <v>0.9507191700000001</v>
       </c>
       <c r="P18">
-        <v>8.6587128</v>
+        <v>8.556472530000001</v>
       </c>
       <c r="Q18">
-        <v>17.5887128</v>
+        <v>17.48647253</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07953506266055052</v>
+        <v>0.07990681254293977</v>
       </c>
       <c r="T18">
-        <v>0.5218706903231313</v>
+        <v>0.5276215427730629</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.638655044686477</v>
+        <v>7.0834023597136</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07463055441064001</v>
+        <v>0.07463245618641759</v>
       </c>
       <c r="C19">
-        <v>169.4864605151906</v>
+        <v>167.7814219274109</v>
       </c>
       <c r="D19">
-        <v>198.1234605151906</v>
+        <v>198.1114219274109</v>
       </c>
       <c r="E19">
-        <v>-23.119</v>
+        <v>-21.42599999999999</v>
       </c>
       <c r="F19">
-        <v>28.781</v>
+        <v>30.47400000000001</v>
       </c>
       <c r="G19">
         <v>0.144</v>
@@ -2839,28 +2839,28 @@
         <v>11.07</v>
       </c>
       <c r="M19">
-        <v>1.5628083</v>
+        <v>1.6547382</v>
       </c>
       <c r="N19">
-        <v>9.5071917</v>
+        <v>9.4152618</v>
       </c>
       <c r="O19">
-        <v>0.9507191700000001</v>
+        <v>0.94152618</v>
       </c>
       <c r="P19">
-        <v>8.556472530000001</v>
+        <v>8.473735619999999</v>
       </c>
       <c r="Q19">
-        <v>17.48647253</v>
+        <v>17.40373562</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07990681254293977</v>
+        <v>0.0802876294956312</v>
       </c>
       <c r="T19">
-        <v>0.5276215427730629</v>
+        <v>0.5335126599168953</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.0834023597136</v>
+        <v>6.689880006396177</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07463245618641759</v>
+        <v>0.07463435796219517</v>
       </c>
       <c r="C20">
-        <v>167.7814219274109</v>
+        <v>166.0763848025452</v>
       </c>
       <c r="D20">
-        <v>198.1114219274109</v>
+        <v>198.0993848025452</v>
       </c>
       <c r="E20">
-        <v>-21.426</v>
+        <v>-19.733</v>
       </c>
       <c r="F20">
-        <v>30.474</v>
+        <v>32.167</v>
       </c>
       <c r="G20">
         <v>0.144</v>
@@ -2921,28 +2921,28 @@
         <v>11.07</v>
       </c>
       <c r="M20">
-        <v>1.6547382</v>
+        <v>1.7466681</v>
       </c>
       <c r="N20">
-        <v>9.4152618</v>
+        <v>9.323331899999999</v>
       </c>
       <c r="O20">
-        <v>0.94152618</v>
+        <v>0.93233319</v>
       </c>
       <c r="P20">
-        <v>8.473735619999999</v>
+        <v>8.39099871</v>
       </c>
       <c r="Q20">
-        <v>17.40373562</v>
+        <v>17.32099871</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0802876294956312</v>
+        <v>0.08067784933604341</v>
       </c>
       <c r="T20">
-        <v>0.5335126599168953</v>
+        <v>0.5395492367432915</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.689880006396178</v>
+        <v>6.337781058691115</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07463435796219517</v>
+        <v>0.07481625973797276</v>
       </c>
       <c r="C21">
-        <v>166.0763848025452</v>
+        <v>163.2387751803116</v>
       </c>
       <c r="D21">
-        <v>198.0993848025452</v>
+        <v>196.9547751803116</v>
       </c>
       <c r="E21">
-        <v>-19.733</v>
+        <v>-18.03999999999999</v>
       </c>
       <c r="F21">
-        <v>32.167</v>
+        <v>33.86000000000001</v>
       </c>
       <c r="G21">
         <v>0.144</v>
@@ -3003,45 +3003,45 @@
         <v>11.07</v>
       </c>
       <c r="M21">
-        <v>1.7466681</v>
+        <v>1.872458</v>
       </c>
       <c r="N21">
-        <v>9.323331899999999</v>
+        <v>9.197542</v>
       </c>
       <c r="O21">
-        <v>0.93233319</v>
+        <v>0.9197542000000001</v>
       </c>
       <c r="P21">
-        <v>8.39099871</v>
+        <v>8.2777878</v>
       </c>
       <c r="Q21">
-        <v>17.32099871</v>
+        <v>17.2077878</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08067784933604341</v>
+        <v>0.08107782467246594</v>
       </c>
       <c r="T21">
-        <v>0.5395492367432915</v>
+        <v>0.5457367279903477</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.337781058691115</v>
+        <v>5.912015115959877</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07481625973797276</v>
+        <v>0.07482716151375032</v>
       </c>
       <c r="C22">
-        <v>163.2387751803116</v>
+        <v>161.4775961652236</v>
       </c>
       <c r="D22">
-        <v>196.9547751803116</v>
+        <v>196.8865961652236</v>
       </c>
       <c r="E22">
-        <v>-18.03999999999999</v>
+        <v>-16.34699999999999</v>
       </c>
       <c r="F22">
-        <v>33.86000000000001</v>
+        <v>35.553</v>
       </c>
       <c r="G22">
         <v>0.144</v>
@@ -3085,28 +3085,28 @@
         <v>11.07</v>
       </c>
       <c r="M22">
-        <v>1.872458</v>
+        <v>1.9660809</v>
       </c>
       <c r="N22">
-        <v>9.197542</v>
+        <v>9.103919100000001</v>
       </c>
       <c r="O22">
-        <v>0.9197542000000001</v>
+        <v>0.9103919100000001</v>
       </c>
       <c r="P22">
-        <v>8.2777878</v>
+        <v>8.193527190000001</v>
       </c>
       <c r="Q22">
-        <v>17.2077878</v>
+        <v>17.12352719</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08107782467246594</v>
+        <v>0.08148792596677257</v>
       </c>
       <c r="T22">
-        <v>0.5457367279903477</v>
+        <v>0.5520808645854305</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.912015115959877</v>
+        <v>5.630490586628454</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07482716151375032</v>
+        <v>0.0748380632895279</v>
       </c>
       <c r="C23">
-        <v>161.4775961652236</v>
+        <v>159.7164643362933</v>
       </c>
       <c r="D23">
-        <v>196.8865961652236</v>
+        <v>196.8184643362933</v>
       </c>
       <c r="E23">
-        <v>-16.34699999999999</v>
+        <v>-14.654</v>
       </c>
       <c r="F23">
-        <v>35.553</v>
+        <v>37.246</v>
       </c>
       <c r="G23">
         <v>0.144</v>
@@ -3167,28 +3167,28 @@
         <v>11.07</v>
       </c>
       <c r="M23">
-        <v>1.9660809</v>
+        <v>2.0597038</v>
       </c>
       <c r="N23">
-        <v>9.103919100000001</v>
+        <v>9.010296199999999</v>
       </c>
       <c r="O23">
-        <v>0.9103919100000001</v>
+        <v>0.90102962</v>
       </c>
       <c r="P23">
-        <v>8.193527190000001</v>
+        <v>8.10926658</v>
       </c>
       <c r="Q23">
-        <v>17.12352719</v>
+        <v>17.03926658</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08148792596677257</v>
+        <v>0.08190854267888192</v>
       </c>
       <c r="T23">
-        <v>0.5520808645854305</v>
+        <v>0.558587671349618</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.630490586628454</v>
+        <v>5.37455919632716</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0748380632895279</v>
+        <v>0.07484896506530549</v>
       </c>
       <c r="C24">
-        <v>159.7164643362933</v>
+        <v>157.9553796445518</v>
       </c>
       <c r="D24">
-        <v>196.8184643362933</v>
+        <v>196.7503796445518</v>
       </c>
       <c r="E24">
-        <v>-14.654</v>
+        <v>-12.96099999999999</v>
       </c>
       <c r="F24">
-        <v>37.246</v>
+        <v>38.93900000000001</v>
       </c>
       <c r="G24">
         <v>0.144</v>
@@ -3249,28 +3249,28 @@
         <v>11.07</v>
       </c>
       <c r="M24">
-        <v>2.0597038</v>
+        <v>2.1533267</v>
       </c>
       <c r="N24">
-        <v>9.010296199999999</v>
+        <v>8.916673299999999</v>
       </c>
       <c r="O24">
-        <v>0.90102962</v>
+        <v>0.89166733</v>
       </c>
       <c r="P24">
-        <v>8.10926658</v>
+        <v>8.025005969999999</v>
       </c>
       <c r="Q24">
-        <v>17.03926658</v>
+        <v>16.95500597</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08190854267888192</v>
+        <v>0.08234008450039673</v>
       </c>
       <c r="T24">
-        <v>0.558587671349618</v>
+        <v>0.5652634860817065</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.37455919632716</v>
+        <v>5.140882709530327</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07484896506530549</v>
+        <v>0.07485986684108308</v>
       </c>
       <c r="C25">
-        <v>157.9553796445518</v>
+        <v>156.1943420410983</v>
       </c>
       <c r="D25">
-        <v>196.7503796445518</v>
+        <v>196.6823420410983</v>
       </c>
       <c r="E25">
-        <v>-12.96099999999999</v>
+        <v>-11.26799999999999</v>
       </c>
       <c r="F25">
-        <v>38.93900000000001</v>
+        <v>40.63200000000001</v>
       </c>
       <c r="G25">
         <v>0.144</v>
@@ -3331,28 +3331,28 @@
         <v>11.07</v>
       </c>
       <c r="M25">
-        <v>2.1533267</v>
+        <v>2.2469496</v>
       </c>
       <c r="N25">
-        <v>8.916673299999999</v>
+        <v>8.8230504</v>
       </c>
       <c r="O25">
-        <v>0.89166733</v>
+        <v>0.88230504</v>
       </c>
       <c r="P25">
-        <v>8.025005969999999</v>
+        <v>7.940745359999999</v>
       </c>
       <c r="Q25">
-        <v>16.95500597</v>
+        <v>16.87074536</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08234008450039673</v>
+        <v>0.08278298268563561</v>
       </c>
       <c r="T25">
-        <v>0.5652634860817065</v>
+        <v>0.57211498014885</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.140882709530327</v>
+        <v>4.926679263299897</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07485986684108308</v>
+        <v>0.07487076861686064</v>
       </c>
       <c r="C26">
-        <v>156.1943420410983</v>
+        <v>154.4333514770992</v>
       </c>
       <c r="D26">
-        <v>196.6823420410983</v>
+        <v>196.6143514770992</v>
       </c>
       <c r="E26">
-        <v>-11.268</v>
+        <v>-9.574999999999996</v>
       </c>
       <c r="F26">
-        <v>40.632</v>
+        <v>42.325</v>
       </c>
       <c r="G26">
         <v>0.144</v>
@@ -3413,28 +3413,28 @@
         <v>11.07</v>
       </c>
       <c r="M26">
-        <v>2.2469496</v>
+        <v>2.3405725</v>
       </c>
       <c r="N26">
-        <v>8.8230504</v>
+        <v>8.7294275</v>
       </c>
       <c r="O26">
-        <v>0.88230504</v>
+        <v>0.87294275</v>
       </c>
       <c r="P26">
-        <v>7.940745359999999</v>
+        <v>7.85648475</v>
       </c>
       <c r="Q26">
-        <v>16.87074536</v>
+        <v>16.78648475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08278298268563561</v>
+        <v>0.08323769148914752</v>
       </c>
       <c r="T26">
-        <v>0.57211498014885</v>
+        <v>0.5791491807244505</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.926679263299897</v>
+        <v>4.729612092767901</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07487076861686064</v>
+        <v>0.07488167039263821</v>
       </c>
       <c r="C27">
-        <v>154.4333514770992</v>
+        <v>152.6724079037886</v>
       </c>
       <c r="D27">
-        <v>196.6143514770992</v>
+        <v>196.5464079037886</v>
       </c>
       <c r="E27">
-        <v>-9.574999999999996</v>
+        <v>-7.881999999999991</v>
       </c>
       <c r="F27">
-        <v>42.325</v>
+        <v>44.01800000000001</v>
       </c>
       <c r="G27">
         <v>0.144</v>
@@ -3495,28 +3495,28 @@
         <v>11.07</v>
       </c>
       <c r="M27">
-        <v>2.3405725</v>
+        <v>2.434195400000001</v>
       </c>
       <c r="N27">
-        <v>8.7294275</v>
+        <v>8.6358046</v>
       </c>
       <c r="O27">
-        <v>0.87294275</v>
+        <v>0.8635804600000001</v>
       </c>
       <c r="P27">
-        <v>7.85648475</v>
+        <v>7.772224140000001</v>
       </c>
       <c r="Q27">
-        <v>16.78648475</v>
+        <v>16.70222414</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08323769148914752</v>
+        <v>0.08370468971978137</v>
       </c>
       <c r="T27">
-        <v>0.5791491807244505</v>
+        <v>0.5863734948291215</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.729612092767901</v>
+        <v>4.547703935353751</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07488167039263821</v>
+        <v>0.0755000721684158</v>
       </c>
       <c r="C28">
-        <v>152.6724079037886</v>
+        <v>147.2007205249571</v>
       </c>
       <c r="D28">
-        <v>196.5464079037886</v>
+        <v>192.7677205249571</v>
       </c>
       <c r="E28">
-        <v>-7.881999999999991</v>
+        <v>-6.188999999999993</v>
       </c>
       <c r="F28">
-        <v>44.01800000000001</v>
+        <v>45.71100000000001</v>
       </c>
       <c r="G28">
         <v>0.144</v>
@@ -3577,45 +3577,45 @@
         <v>11.07</v>
       </c>
       <c r="M28">
-        <v>2.434195400000001</v>
+        <v>2.6420958</v>
       </c>
       <c r="N28">
-        <v>8.6358046</v>
+        <v>8.4279042</v>
       </c>
       <c r="O28">
-        <v>0.8635804600000001</v>
+        <v>0.84279042</v>
       </c>
       <c r="P28">
-        <v>7.772224140000001</v>
+        <v>7.58511378</v>
       </c>
       <c r="Q28">
-        <v>16.70222414</v>
+        <v>16.51511378</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08370468971978137</v>
+        <v>0.0841844824224874</v>
       </c>
       <c r="T28">
-        <v>0.5863734948291215</v>
+        <v>0.593795735347619</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.1</v>
       </c>
       <c r="W28">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.547703935353751</v>
+        <v>4.189855644144319</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0755000721684158</v>
+        <v>0.07553347394419338</v>
       </c>
       <c r="C29">
-        <v>147.2007205249571</v>
+        <v>145.3077535649043</v>
       </c>
       <c r="D29">
-        <v>192.7677205249571</v>
+        <v>192.5677535649043</v>
       </c>
       <c r="E29">
-        <v>-6.188999999999993</v>
+        <v>-4.495999999999988</v>
       </c>
       <c r="F29">
-        <v>45.71100000000001</v>
+        <v>47.40400000000001</v>
       </c>
       <c r="G29">
         <v>0.144</v>
@@ -3659,28 +3659,28 @@
         <v>11.07</v>
       </c>
       <c r="M29">
-        <v>2.6420958</v>
+        <v>2.739951200000001</v>
       </c>
       <c r="N29">
-        <v>8.4279042</v>
+        <v>8.3300488</v>
       </c>
       <c r="O29">
-        <v>0.84279042</v>
+        <v>0.8330048800000001</v>
       </c>
       <c r="P29">
-        <v>7.58511378</v>
+        <v>7.49704392</v>
       </c>
       <c r="Q29">
-        <v>16.51511378</v>
+        <v>16.42704392</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0841844824224874</v>
+        <v>0.08467760270026858</v>
       </c>
       <c r="T29">
-        <v>0.593795735347619</v>
+        <v>0.6014241492138526</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.189855644144319</v>
+        <v>4.040217942567736</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07553347394419338</v>
+        <v>0.07648037571997096</v>
       </c>
       <c r="C30">
-        <v>145.3077535649043</v>
+        <v>138.1135779541831</v>
       </c>
       <c r="D30">
-        <v>192.5677535649043</v>
+        <v>187.0665779541831</v>
       </c>
       <c r="E30">
-        <v>-4.495999999999988</v>
+        <v>-2.80299999999999</v>
       </c>
       <c r="F30">
-        <v>47.40400000000001</v>
+        <v>49.09700000000001</v>
       </c>
       <c r="G30">
         <v>0.144</v>
@@ -3741,45 +3741,45 @@
         <v>11.07</v>
       </c>
       <c r="M30">
-        <v>2.739951200000001</v>
+        <v>3.0096461</v>
       </c>
       <c r="N30">
-        <v>8.3300488</v>
+        <v>8.060353899999999</v>
       </c>
       <c r="O30">
-        <v>0.8330048800000001</v>
+        <v>0.8060353899999999</v>
       </c>
       <c r="P30">
-        <v>7.49704392</v>
+        <v>7.254318509999999</v>
       </c>
       <c r="Q30">
-        <v>16.42704392</v>
+        <v>16.18431851</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08467760270026858</v>
+        <v>0.08518461369009994</v>
       </c>
       <c r="T30">
-        <v>0.6014241492138526</v>
+        <v>0.6092674479777265</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.040217942567736</v>
+        <v>3.678173324099467</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07648037571997096</v>
+        <v>0.07654527749574852</v>
       </c>
       <c r="C31">
-        <v>138.1135779541831</v>
+        <v>136.0550082000401</v>
       </c>
       <c r="D31">
-        <v>187.0665779541831</v>
+        <v>186.7010082000401</v>
       </c>
       <c r="E31">
-        <v>-2.802999999999997</v>
+        <v>-1.109999999999999</v>
       </c>
       <c r="F31">
-        <v>49.097</v>
+        <v>50.79</v>
       </c>
       <c r="G31">
         <v>0.144</v>
@@ -3823,28 +3823,28 @@
         <v>11.07</v>
       </c>
       <c r="M31">
-        <v>3.0096461</v>
+        <v>3.113427</v>
       </c>
       <c r="N31">
-        <v>8.060353900000001</v>
+        <v>7.956573000000001</v>
       </c>
       <c r="O31">
-        <v>0.8060353900000001</v>
+        <v>0.7956573000000001</v>
       </c>
       <c r="P31">
-        <v>7.254318510000001</v>
+        <v>7.1609157</v>
       </c>
       <c r="Q31">
-        <v>16.18431851</v>
+        <v>16.0909157</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08518461369009994</v>
+        <v>0.08570611070821219</v>
       </c>
       <c r="T31">
-        <v>0.6092674479777264</v>
+        <v>0.6173348409919968</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.678173324099468</v>
+        <v>3.555567546629486</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07654527749574852</v>
+        <v>0.07739137927152612</v>
       </c>
       <c r="C32">
-        <v>136.0550082000401</v>
+        <v>129.7236848130617</v>
       </c>
       <c r="D32">
-        <v>186.7010082000401</v>
+        <v>182.0626848130617</v>
       </c>
       <c r="E32">
-        <v>-1.109999999999999</v>
+        <v>0.5830000000000055</v>
       </c>
       <c r="F32">
-        <v>50.79</v>
+        <v>52.483</v>
       </c>
       <c r="G32">
         <v>0.144</v>
@@ -3905,45 +3905,45 @@
         <v>11.07</v>
       </c>
       <c r="M32">
-        <v>3.113427</v>
+        <v>3.3641603</v>
       </c>
       <c r="N32">
-        <v>7.956573000000001</v>
+        <v>7.7058397</v>
       </c>
       <c r="O32">
-        <v>0.7956573000000001</v>
+        <v>0.7705839700000001</v>
       </c>
       <c r="P32">
-        <v>7.1609157</v>
+        <v>6.93525573</v>
       </c>
       <c r="Q32">
-        <v>16.0909157</v>
+        <v>15.86525573</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08570611070821219</v>
+        <v>0.08624272358192191</v>
       </c>
       <c r="T32">
-        <v>0.6173348409919968</v>
+        <v>0.6256360714849416</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.555567546629486</v>
+        <v>3.290568526119281</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07739137927152612</v>
+        <v>0.07748148104730368</v>
       </c>
       <c r="C33">
-        <v>129.7236848130617</v>
+        <v>127.5502896860257</v>
       </c>
       <c r="D33">
-        <v>182.0626848130617</v>
+        <v>181.5822896860257</v>
       </c>
       <c r="E33">
-        <v>0.5830000000000055</v>
+        <v>2.276000000000003</v>
       </c>
       <c r="F33">
-        <v>52.483</v>
+        <v>54.176</v>
       </c>
       <c r="G33">
         <v>0.144</v>
@@ -3987,28 +3987,28 @@
         <v>11.07</v>
       </c>
       <c r="M33">
-        <v>3.3641603</v>
+        <v>3.4726816</v>
       </c>
       <c r="N33">
-        <v>7.7058397</v>
+        <v>7.5973184</v>
       </c>
       <c r="O33">
-        <v>0.7705839700000001</v>
+        <v>0.75973184</v>
       </c>
       <c r="P33">
-        <v>6.93525573</v>
+        <v>6.83758656</v>
       </c>
       <c r="Q33">
-        <v>15.86525573</v>
+        <v>15.76758656</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08624272358192191</v>
+        <v>0.08679511918721131</v>
       </c>
       <c r="T33">
-        <v>0.6256360714849416</v>
+        <v>0.6341814558159142</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.290568526119281</v>
+        <v>3.187738259678054</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07748148104730368</v>
+        <v>0.07757158282308127</v>
       </c>
       <c r="C34">
-        <v>127.5502896860257</v>
+        <v>125.3794230522982</v>
       </c>
       <c r="D34">
-        <v>181.5822896860257</v>
+        <v>181.1044230522982</v>
       </c>
       <c r="E34">
-        <v>2.276000000000003</v>
+        <v>3.969000000000008</v>
       </c>
       <c r="F34">
-        <v>54.176</v>
+        <v>55.86900000000001</v>
       </c>
       <c r="G34">
         <v>0.144</v>
@@ -4069,28 +4069,28 @@
         <v>11.07</v>
       </c>
       <c r="M34">
-        <v>3.4726816</v>
+        <v>3.581202900000001</v>
       </c>
       <c r="N34">
-        <v>7.5973184</v>
+        <v>7.488797099999999</v>
       </c>
       <c r="O34">
-        <v>0.75973184</v>
+        <v>0.74887971</v>
       </c>
       <c r="P34">
-        <v>6.83758656</v>
+        <v>6.73991739</v>
       </c>
       <c r="Q34">
-        <v>15.76758656</v>
+        <v>15.66991739</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08679511918721131</v>
+        <v>0.08736400421355414</v>
       </c>
       <c r="T34">
-        <v>0.6341814558159142</v>
+        <v>0.6429819262463188</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.187738259678054</v>
+        <v>3.0911401305969</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07757158282308127</v>
+        <v>0.07766168459885885</v>
       </c>
       <c r="C35">
-        <v>125.3794230522982</v>
+        <v>123.2110650017143</v>
       </c>
       <c r="D35">
-        <v>181.1044230522982</v>
+        <v>180.6290650017143</v>
       </c>
       <c r="E35">
-        <v>3.969000000000008</v>
+        <v>5.662000000000006</v>
       </c>
       <c r="F35">
-        <v>55.86900000000001</v>
+        <v>57.562</v>
       </c>
       <c r="G35">
         <v>0.144</v>
@@ -4151,28 +4151,28 @@
         <v>11.07</v>
       </c>
       <c r="M35">
-        <v>3.581202900000001</v>
+        <v>3.689724200000001</v>
       </c>
       <c r="N35">
-        <v>7.488797099999999</v>
+        <v>7.3802758</v>
       </c>
       <c r="O35">
-        <v>0.74887971</v>
+        <v>0.73802758</v>
       </c>
       <c r="P35">
-        <v>6.73991739</v>
+        <v>6.64224822</v>
       </c>
       <c r="Q35">
-        <v>15.66991739</v>
+        <v>15.57224822</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08736400421355414</v>
+        <v>0.08795012818008917</v>
       </c>
       <c r="T35">
-        <v>0.6429819262463188</v>
+        <v>0.652049077598857</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.0911401305969</v>
+        <v>3.000224244402874</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07766168459885885</v>
+        <v>0.08020878637463644</v>
       </c>
       <c r="C36">
-        <v>123.2110650017143</v>
+        <v>109.0411512645935</v>
       </c>
       <c r="D36">
-        <v>180.6290650017143</v>
+        <v>168.1521512645935</v>
       </c>
       <c r="E36">
-        <v>5.662000000000006</v>
+        <v>7.355000000000011</v>
       </c>
       <c r="F36">
-        <v>57.562</v>
+        <v>59.25500000000001</v>
       </c>
       <c r="G36">
         <v>0.144</v>
@@ -4233,45 +4233,45 @@
         <v>11.07</v>
       </c>
       <c r="M36">
-        <v>3.689724200000001</v>
+        <v>4.260434500000001</v>
       </c>
       <c r="N36">
-        <v>7.3802758</v>
+        <v>6.809565499999999</v>
       </c>
       <c r="O36">
-        <v>0.73802758</v>
+        <v>0.6809565499999999</v>
       </c>
       <c r="P36">
-        <v>6.64224822</v>
+        <v>6.128608949999999</v>
       </c>
       <c r="Q36">
-        <v>15.57224822</v>
+        <v>15.05860895</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08795012818008917</v>
+        <v>0.0885542867302099</v>
       </c>
       <c r="T36">
-        <v>0.652049077598857</v>
+        <v>0.6613952182237809</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.1</v>
       </c>
       <c r="W36">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.000224244402874</v>
+        <v>2.598326532188207</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08020878637463644</v>
+        <v>0.08036908815041401</v>
       </c>
       <c r="C37">
-        <v>109.0411512645935</v>
+        <v>106.6203209846273</v>
       </c>
       <c r="D37">
-        <v>168.1521512645935</v>
+        <v>167.4243209846273</v>
       </c>
       <c r="E37">
-        <v>7.355000000000011</v>
+        <v>9.048000000000016</v>
       </c>
       <c r="F37">
-        <v>59.25500000000001</v>
+        <v>60.94800000000001</v>
       </c>
       <c r="G37">
         <v>0.144</v>
@@ -4315,28 +4315,28 @@
         <v>11.07</v>
       </c>
       <c r="M37">
-        <v>4.260434500000001</v>
+        <v>4.382161200000001</v>
       </c>
       <c r="N37">
-        <v>6.809565499999999</v>
+        <v>6.687838799999999</v>
       </c>
       <c r="O37">
-        <v>0.6809565499999999</v>
+        <v>0.6687838799999999</v>
       </c>
       <c r="P37">
-        <v>6.128608949999999</v>
+        <v>6.019054919999999</v>
       </c>
       <c r="Q37">
-        <v>15.05860895</v>
+        <v>14.94905492</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0885542867302099</v>
+        <v>0.08917732523502189</v>
       </c>
       <c r="T37">
-        <v>0.6613952182237809</v>
+        <v>0.6710334257432337</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.598326532188207</v>
+        <v>2.526150795182979</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08036908815041402</v>
+        <v>0.08182808992619159</v>
       </c>
       <c r="C38">
-        <v>106.6203209846272</v>
+        <v>98.58157114622718</v>
       </c>
       <c r="D38">
-        <v>167.4243209846272</v>
+        <v>161.0785711462272</v>
       </c>
       <c r="E38">
-        <v>9.048000000000002</v>
+        <v>10.74100000000001</v>
       </c>
       <c r="F38">
-        <v>60.948</v>
+        <v>62.64100000000001</v>
       </c>
       <c r="G38">
         <v>0.144</v>
@@ -4397,45 +4397,45 @@
         <v>11.07</v>
       </c>
       <c r="M38">
-        <v>4.382161200000001</v>
+        <v>4.748187800000001</v>
       </c>
       <c r="N38">
-        <v>6.6878388</v>
+        <v>6.321812199999999</v>
       </c>
       <c r="O38">
-        <v>0.66878388</v>
+        <v>0.63218122</v>
       </c>
       <c r="P38">
-        <v>6.019054919999999</v>
+        <v>5.68963098</v>
       </c>
       <c r="Q38">
-        <v>14.94905492</v>
+        <v>14.61963098</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08917732523502189</v>
+        <v>0.08982014273998665</v>
       </c>
       <c r="T38">
-        <v>0.6710334257432337</v>
+        <v>0.6809776081045736</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.1</v>
       </c>
       <c r="W38">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.526150795182979</v>
+        <v>2.331415787724318</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08182808992619159</v>
+        <v>0.08202349170196917</v>
       </c>
       <c r="C39">
-        <v>98.58157114622718</v>
+        <v>96.07503683448667</v>
       </c>
       <c r="D39">
-        <v>161.0785711462272</v>
+        <v>160.2650368344867</v>
       </c>
       <c r="E39">
-        <v>10.74100000000001</v>
+        <v>12.434</v>
       </c>
       <c r="F39">
-        <v>62.64100000000001</v>
+        <v>64.334</v>
       </c>
       <c r="G39">
         <v>0.144</v>
@@ -4479,28 +4479,28 @@
         <v>11.07</v>
       </c>
       <c r="M39">
-        <v>4.748187800000001</v>
+        <v>4.8765172</v>
       </c>
       <c r="N39">
-        <v>6.321812199999999</v>
+        <v>6.1934828</v>
       </c>
       <c r="O39">
-        <v>0.63218122</v>
+        <v>0.6193482800000001</v>
       </c>
       <c r="P39">
-        <v>5.68963098</v>
+        <v>5.574134519999999</v>
       </c>
       <c r="Q39">
-        <v>14.61963098</v>
+        <v>14.50413452</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08982014273998665</v>
+        <v>0.09048369629349864</v>
       </c>
       <c r="T39">
-        <v>0.6809776081045736</v>
+        <v>0.6912425705420862</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.331415787724318</v>
+        <v>2.270062740678942</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08202349170196917</v>
+        <v>0.08221889347774673</v>
       </c>
       <c r="C40">
-        <v>96.07503683448667</v>
+        <v>93.57667880873011</v>
       </c>
       <c r="D40">
-        <v>160.2650368344867</v>
+        <v>159.4596788087301</v>
       </c>
       <c r="E40">
-        <v>12.434</v>
+        <v>14.127</v>
       </c>
       <c r="F40">
-        <v>64.334</v>
+        <v>66.027</v>
       </c>
       <c r="G40">
         <v>0.144</v>
@@ -4561,28 +4561,28 @@
         <v>11.07</v>
       </c>
       <c r="M40">
-        <v>4.8765172</v>
+        <v>5.0048466</v>
       </c>
       <c r="N40">
-        <v>6.1934828</v>
+        <v>6.0651534</v>
       </c>
       <c r="O40">
-        <v>0.6193482800000001</v>
+        <v>0.6065153400000001</v>
       </c>
       <c r="P40">
-        <v>5.574134519999999</v>
+        <v>5.45863806</v>
       </c>
       <c r="Q40">
-        <v>14.50413452</v>
+        <v>14.38863806</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09048369629349864</v>
+        <v>0.09116900570122416</v>
       </c>
       <c r="T40">
-        <v>0.6912425705420862</v>
+        <v>0.7018440891250908</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.270062740678942</v>
+        <v>2.211856003738456</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08221889347774673</v>
+        <v>0.08241429525352433</v>
       </c>
       <c r="C41">
-        <v>93.57667880873011</v>
+        <v>91.08637442374602</v>
       </c>
       <c r="D41">
-        <v>159.4596788087301</v>
+        <v>158.662374423746</v>
       </c>
       <c r="E41">
-        <v>14.127</v>
+        <v>15.82000000000001</v>
       </c>
       <c r="F41">
-        <v>66.027</v>
+        <v>67.72000000000001</v>
       </c>
       <c r="G41">
         <v>0.144</v>
@@ -4643,28 +4643,28 @@
         <v>11.07</v>
       </c>
       <c r="M41">
-        <v>5.0048466</v>
+        <v>5.133176000000002</v>
       </c>
       <c r="N41">
-        <v>6.0651534</v>
+        <v>5.936823999999999</v>
       </c>
       <c r="O41">
-        <v>0.6065153400000001</v>
+        <v>0.5936823999999999</v>
       </c>
       <c r="P41">
-        <v>5.45863806</v>
+        <v>5.343141599999999</v>
       </c>
       <c r="Q41">
-        <v>14.38863806</v>
+        <v>14.2731416</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09116900570122416</v>
+        <v>0.09187715875587388</v>
       </c>
       <c r="T41">
-        <v>0.7018440891250908</v>
+        <v>0.7127989916608622</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.211856003738456</v>
+        <v>2.156559603644994</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08241429525352433</v>
+        <v>0.0826096970293019</v>
       </c>
       <c r="C42">
-        <v>91.08637442374602</v>
+        <v>88.60400347504222</v>
       </c>
       <c r="D42">
-        <v>158.662374423746</v>
+        <v>157.8730034750422</v>
       </c>
       <c r="E42">
-        <v>15.82000000000001</v>
+        <v>17.51300000000001</v>
       </c>
       <c r="F42">
-        <v>67.72000000000001</v>
+        <v>69.41300000000001</v>
       </c>
       <c r="G42">
         <v>0.144</v>
@@ -4725,28 +4725,28 @@
         <v>11.07</v>
       </c>
       <c r="M42">
-        <v>5.133176000000002</v>
+        <v>5.261505400000002</v>
       </c>
       <c r="N42">
-        <v>5.936823999999999</v>
+        <v>5.808494599999999</v>
       </c>
       <c r="O42">
-        <v>0.5936823999999999</v>
+        <v>0.5808494599999999</v>
       </c>
       <c r="P42">
-        <v>5.343141599999999</v>
+        <v>5.227645139999999</v>
       </c>
       <c r="Q42">
-        <v>14.2731416</v>
+        <v>14.15764514</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09187715875587388</v>
+        <v>0.09260931699881678</v>
       </c>
       <c r="T42">
-        <v>0.7127989916608622</v>
+        <v>0.7241252468249649</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.156559603644994</v>
+        <v>2.103960588921946</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0826096970293019</v>
+        <v>0.08280509880507948</v>
       </c>
       <c r="C43">
-        <v>88.60400347504222</v>
+        <v>86.12944813843099</v>
       </c>
       <c r="D43">
-        <v>157.8730034750422</v>
+        <v>157.091448138431</v>
       </c>
       <c r="E43">
-        <v>17.51300000000001</v>
+        <v>19.20600000000001</v>
       </c>
       <c r="F43">
-        <v>69.41300000000001</v>
+        <v>71.10600000000001</v>
       </c>
       <c r="G43">
         <v>0.144</v>
@@ -4807,28 +4807,28 @@
         <v>11.07</v>
       </c>
       <c r="M43">
-        <v>5.261505400000002</v>
+        <v>5.389834800000001</v>
       </c>
       <c r="N43">
-        <v>5.808494599999999</v>
+        <v>5.680165199999999</v>
       </c>
       <c r="O43">
-        <v>0.5808494599999999</v>
+        <v>0.5680165199999999</v>
       </c>
       <c r="P43">
-        <v>5.227645139999999</v>
+        <v>5.11214868</v>
       </c>
       <c r="Q43">
-        <v>14.15764514</v>
+        <v>14.04214868</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09260931699881678</v>
+        <v>0.09336672207772324</v>
       </c>
       <c r="T43">
-        <v>0.7241252468249649</v>
+        <v>0.7358420625119677</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.103960588921946</v>
+        <v>2.053866289185709</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08280509880507948</v>
+        <v>0.08300050058085706</v>
       </c>
       <c r="C44">
-        <v>86.12944813843099</v>
+        <v>83.66259291140076</v>
       </c>
       <c r="D44">
-        <v>157.091448138431</v>
+        <v>156.3175929114008</v>
       </c>
       <c r="E44">
-        <v>19.20600000000001</v>
+        <v>20.89900000000001</v>
       </c>
       <c r="F44">
-        <v>71.10600000000001</v>
+        <v>72.79900000000001</v>
       </c>
       <c r="G44">
         <v>0.144</v>
@@ -4889,28 +4889,28 @@
         <v>11.07</v>
       </c>
       <c r="M44">
-        <v>5.389834800000001</v>
+        <v>5.518164200000001</v>
       </c>
       <c r="N44">
-        <v>5.680165199999999</v>
+        <v>5.551835799999999</v>
       </c>
       <c r="O44">
-        <v>0.5680165199999999</v>
+        <v>0.5551835799999999</v>
       </c>
       <c r="P44">
-        <v>5.11214868</v>
+        <v>4.99665222</v>
       </c>
       <c r="Q44">
-        <v>14.04214868</v>
+        <v>13.92665222</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09336672207772323</v>
+        <v>0.09415070277343343</v>
       </c>
       <c r="T44">
-        <v>0.7358420625119676</v>
+        <v>0.7479699945388653</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.053866289185709</v>
+        <v>2.006101956879065</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08300050058085706</v>
+        <v>0.08881910235663465</v>
       </c>
       <c r="C45">
-        <v>83.66259291140076</v>
+        <v>61.97283681396392</v>
       </c>
       <c r="D45">
-        <v>156.3175929114008</v>
+        <v>136.3208368139639</v>
       </c>
       <c r="E45">
-        <v>20.89900000000001</v>
+        <v>22.59200000000001</v>
       </c>
       <c r="F45">
-        <v>72.79900000000001</v>
+        <v>74.492</v>
       </c>
       <c r="G45">
         <v>0.144</v>
@@ -4971,45 +4971,45 @@
         <v>11.07</v>
       </c>
       <c r="M45">
-        <v>5.518164200000001</v>
+        <v>6.70428</v>
       </c>
       <c r="N45">
-        <v>5.551835799999999</v>
+        <v>4.36572</v>
       </c>
       <c r="O45">
-        <v>0.5551835799999999</v>
+        <v>0.4365720000000001</v>
       </c>
       <c r="P45">
-        <v>4.99665222</v>
+        <v>3.929148000000001</v>
       </c>
       <c r="Q45">
-        <v>13.92665222</v>
+        <v>12.859148</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09415070277343343</v>
+        <v>0.09496268277970471</v>
       </c>
       <c r="T45">
-        <v>0.7479699945388653</v>
+        <v>0.760531066995295</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.1</v>
       </c>
       <c r="W45">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.006101956879065</v>
+        <v>1.651184019760511</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08881910235663465</v>
+        <v>0.08914230413241223</v>
       </c>
       <c r="C46">
-        <v>61.97283681396392</v>
+        <v>59.3180164149905</v>
       </c>
       <c r="D46">
-        <v>136.3208368139639</v>
+        <v>135.3590164149905</v>
       </c>
       <c r="E46">
-        <v>22.59200000000001</v>
+        <v>24.285</v>
       </c>
       <c r="F46">
-        <v>74.492</v>
+        <v>76.185</v>
       </c>
       <c r="G46">
         <v>0.144</v>
@@ -5053,28 +5053,28 @@
         <v>11.07</v>
       </c>
       <c r="M46">
-        <v>6.70428</v>
+        <v>6.85665</v>
       </c>
       <c r="N46">
-        <v>4.36572</v>
+        <v>4.21335</v>
       </c>
       <c r="O46">
-        <v>0.4365720000000001</v>
+        <v>0.421335</v>
       </c>
       <c r="P46">
-        <v>3.929148000000001</v>
+        <v>3.792015</v>
       </c>
       <c r="Q46">
-        <v>12.859148</v>
+        <v>12.722015</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09496268277970471</v>
+        <v>0.09580418933165857</v>
       </c>
       <c r="T46">
-        <v>0.760531066995295</v>
+        <v>0.7735489057228675</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.651184019760511</v>
+        <v>1.614491041543611</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08914230413241223</v>
+        <v>0.0894655059081898</v>
       </c>
       <c r="C47">
-        <v>59.3180164149905</v>
+        <v>56.67667329710503</v>
       </c>
       <c r="D47">
-        <v>135.3590164149905</v>
+        <v>134.410673297105</v>
       </c>
       <c r="E47">
-        <v>24.285</v>
+        <v>25.97800000000002</v>
       </c>
       <c r="F47">
-        <v>76.185</v>
+        <v>77.87800000000001</v>
       </c>
       <c r="G47">
         <v>0.144</v>
@@ -5135,28 +5135,28 @@
         <v>11.07</v>
       </c>
       <c r="M47">
-        <v>6.85665</v>
+        <v>7.009020000000001</v>
       </c>
       <c r="N47">
-        <v>4.21335</v>
+        <v>4.060979999999999</v>
       </c>
       <c r="O47">
-        <v>0.421335</v>
+        <v>0.4060979999999999</v>
       </c>
       <c r="P47">
-        <v>3.792015</v>
+        <v>3.654881999999999</v>
       </c>
       <c r="Q47">
-        <v>12.722015</v>
+        <v>12.584882</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09580418933165857</v>
+        <v>0.09667686279294406</v>
       </c>
       <c r="T47">
-        <v>0.7735489057228675</v>
+        <v>0.7870488866255353</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.614491041543611</v>
+        <v>1.579393410205706</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0894655059081898</v>
+        <v>0.08978870768396738</v>
       </c>
       <c r="C48">
-        <v>56.67667329710503</v>
+        <v>54.04852616030705</v>
       </c>
       <c r="D48">
-        <v>134.410673297105</v>
+        <v>133.4755261603071</v>
       </c>
       <c r="E48">
-        <v>25.97800000000002</v>
+        <v>27.67100000000001</v>
       </c>
       <c r="F48">
-        <v>77.87800000000001</v>
+        <v>79.57100000000001</v>
       </c>
       <c r="G48">
         <v>0.144</v>
@@ -5217,28 +5217,28 @@
         <v>11.07</v>
       </c>
       <c r="M48">
-        <v>7.009020000000001</v>
+        <v>7.161390000000001</v>
       </c>
       <c r="N48">
-        <v>4.060979999999999</v>
+        <v>3.908609999999999</v>
       </c>
       <c r="O48">
-        <v>0.4060979999999999</v>
+        <v>0.390861</v>
       </c>
       <c r="P48">
-        <v>3.654881999999999</v>
+        <v>3.517748999999999</v>
       </c>
       <c r="Q48">
-        <v>12.584882</v>
+        <v>12.447749</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09667686279294406</v>
+        <v>0.09758246732824033</v>
       </c>
       <c r="T48">
-        <v>0.7870488866255353</v>
+        <v>0.8010583007698134</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.579393410205706</v>
+        <v>1.545789295094947</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08978870768396738</v>
+        <v>0.09011190945974495</v>
       </c>
       <c r="C49">
-        <v>54.04852616030705</v>
+        <v>51.43330147895927</v>
       </c>
       <c r="D49">
-        <v>133.4755261603071</v>
+        <v>132.5533014789593</v>
       </c>
       <c r="E49">
-        <v>27.67100000000001</v>
+        <v>29.36400000000001</v>
       </c>
       <c r="F49">
-        <v>79.57100000000001</v>
+        <v>81.26400000000001</v>
       </c>
       <c r="G49">
         <v>0.144</v>
@@ -5299,28 +5299,28 @@
         <v>11.07</v>
       </c>
       <c r="M49">
-        <v>7.161390000000001</v>
+        <v>7.31376</v>
       </c>
       <c r="N49">
-        <v>3.908609999999999</v>
+        <v>3.75624</v>
       </c>
       <c r="O49">
-        <v>0.390861</v>
+        <v>0.375624</v>
       </c>
       <c r="P49">
-        <v>3.517748999999999</v>
+        <v>3.380616</v>
       </c>
       <c r="Q49">
-        <v>12.447749</v>
+        <v>12.310616</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09758246732824033</v>
+        <v>0.09852290280720183</v>
       </c>
       <c r="T49">
-        <v>0.8010583007698134</v>
+        <v>0.8156065385350251</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.545789295094947</v>
+        <v>1.513585351447135</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09011190945974495</v>
+        <v>0.1162668200829923</v>
       </c>
       <c r="C50">
-        <v>51.43330147895928</v>
+        <v>2.204351813694203</v>
       </c>
       <c r="D50">
-        <v>132.5533014789593</v>
+        <v>85.01735181369421</v>
       </c>
       <c r="E50">
-        <v>29.364</v>
+        <v>31.05700000000001</v>
       </c>
       <c r="F50">
-        <v>81.264</v>
+        <v>82.95700000000001</v>
       </c>
       <c r="G50">
         <v>0.144</v>
@@ -5381,45 +5381,45 @@
         <v>11.07</v>
       </c>
       <c r="M50">
-        <v>7.313759999999999</v>
+        <v>12.1780876</v>
       </c>
       <c r="N50">
-        <v>3.756240000000001</v>
+        <v>-1.108087600000003</v>
       </c>
       <c r="O50">
-        <v>0.3756240000000001</v>
+        <v>-0.1108087600000003</v>
       </c>
       <c r="P50">
-        <v>3.380616000000001</v>
+        <v>-0.9972788400000026</v>
       </c>
       <c r="Q50">
-        <v>12.310616</v>
+        <v>7.932721159999997</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09852290280720183</v>
+        <v>0.09975197804165467</v>
       </c>
       <c r="T50">
-        <v>0.8156065385350251</v>
+        <v>0.8346199415192452</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1</v>
+        <v>0.09090097200483266</v>
       </c>
       <c r="W50">
-        <v>0.081</v>
+        <v>0.1334557373096906</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.513585351447135</v>
+        <v>0.9090097200483266</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1162668200829923</v>
+        <v>0.1172768200829923</v>
       </c>
       <c r="C51">
-        <v>2.204351813694203</v>
+        <v>-0.649921135865668</v>
       </c>
       <c r="D51">
-        <v>85.01735181369421</v>
+        <v>83.85607886413433</v>
       </c>
       <c r="E51">
-        <v>31.05700000000001</v>
+        <v>32.75000000000001</v>
       </c>
       <c r="F51">
-        <v>82.95700000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="G51">
         <v>0.144</v>
@@ -5463,37 +5463,37 @@
         <v>11.07</v>
       </c>
       <c r="M51">
-        <v>12.1780876</v>
+        <v>12.42662</v>
       </c>
       <c r="N51">
-        <v>-1.108087600000003</v>
+        <v>-1.356620000000001</v>
       </c>
       <c r="O51">
-        <v>-0.1108087600000003</v>
+        <v>-0.1356620000000001</v>
       </c>
       <c r="P51">
-        <v>-0.9972788400000026</v>
+        <v>-1.220958000000001</v>
       </c>
       <c r="Q51">
-        <v>7.932721159999997</v>
+        <v>7.709041999999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09975197804165467</v>
+        <v>0.1008310176024877</v>
       </c>
       <c r="T51">
-        <v>0.8346199415192452</v>
+        <v>0.8513123403496301</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.09090097200483266</v>
+        <v>0.08908295256473603</v>
       </c>
       <c r="W51">
-        <v>0.1334557373096906</v>
+        <v>0.1337226225634968</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9090097200483266</v>
+        <v>0.8908295256473602</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1172768200829923</v>
+        <v>0.1182868200829923</v>
       </c>
       <c r="C52">
-        <v>-0.649921135865668</v>
+        <v>-3.472897348744439</v>
       </c>
       <c r="D52">
-        <v>83.85607886413433</v>
+        <v>82.72610265125556</v>
       </c>
       <c r="E52">
-        <v>32.75000000000001</v>
+        <v>34.443</v>
       </c>
       <c r="F52">
-        <v>84.65000000000001</v>
+        <v>86.343</v>
       </c>
       <c r="G52">
         <v>0.144</v>
@@ -5545,37 +5545,37 @@
         <v>11.07</v>
       </c>
       <c r="M52">
-        <v>12.42662</v>
+        <v>12.6751524</v>
       </c>
       <c r="N52">
-        <v>-1.356620000000001</v>
+        <v>-1.605152400000001</v>
       </c>
       <c r="O52">
-        <v>-0.1356620000000001</v>
+        <v>-0.1605152400000002</v>
       </c>
       <c r="P52">
-        <v>-1.220958000000001</v>
+        <v>-1.444637160000001</v>
       </c>
       <c r="Q52">
-        <v>7.709041999999998</v>
+        <v>7.485362839999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1008310176024877</v>
+        <v>0.1019540995943753</v>
       </c>
       <c r="T52">
-        <v>0.8513123403496301</v>
+        <v>0.8686860615812553</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.08908295256473603</v>
+        <v>0.08733622800464316</v>
       </c>
       <c r="W52">
-        <v>0.1337226225634968</v>
+        <v>0.1339790417289184</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8908295256473602</v>
+        <v>0.8733622800464316</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1182868200829923</v>
+        <v>0.1192968200829923</v>
       </c>
       <c r="C53">
-        <v>-3.472897348744439</v>
+        <v>-6.265825190969593</v>
       </c>
       <c r="D53">
-        <v>82.72610265125556</v>
+        <v>81.62617480903042</v>
       </c>
       <c r="E53">
-        <v>34.443</v>
+        <v>36.13600000000002</v>
       </c>
       <c r="F53">
-        <v>86.343</v>
+        <v>88.03600000000002</v>
       </c>
       <c r="G53">
         <v>0.144</v>
@@ -5627,37 +5627,37 @@
         <v>11.07</v>
       </c>
       <c r="M53">
-        <v>12.6751524</v>
+        <v>12.9236848</v>
       </c>
       <c r="N53">
-        <v>-1.605152400000001</v>
+        <v>-1.853684800000003</v>
       </c>
       <c r="O53">
-        <v>-0.1605152400000002</v>
+        <v>-0.1853684800000004</v>
       </c>
       <c r="P53">
-        <v>-1.444637160000001</v>
+        <v>-1.668316320000003</v>
       </c>
       <c r="Q53">
-        <v>7.485362839999999</v>
+        <v>7.261683679999996</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1019540995943753</v>
+        <v>0.1031239766692581</v>
       </c>
       <c r="T53">
-        <v>0.8686860615812553</v>
+        <v>0.8867836878641981</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.08733622800464316</v>
+        <v>0.08565668515840001</v>
       </c>
       <c r="W53">
-        <v>0.1339790417289184</v>
+        <v>0.1342255986187469</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8733622800464316</v>
+        <v>0.856566851584</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1192968200829923</v>
+        <v>0.1203068200829923</v>
       </c>
       <c r="C54">
-        <v>-6.265825190969593</v>
+        <v>-9.029887506556264</v>
       </c>
       <c r="D54">
-        <v>81.62617480903042</v>
+        <v>80.55511249344374</v>
       </c>
       <c r="E54">
-        <v>36.13600000000002</v>
+        <v>37.82900000000001</v>
       </c>
       <c r="F54">
-        <v>88.03600000000002</v>
+        <v>89.72900000000001</v>
       </c>
       <c r="G54">
         <v>0.144</v>
@@ -5709,37 +5709,37 @@
         <v>11.07</v>
       </c>
       <c r="M54">
-        <v>12.9236848</v>
+        <v>13.1722172</v>
       </c>
       <c r="N54">
-        <v>-1.853684800000003</v>
+        <v>-2.102217200000004</v>
       </c>
       <c r="O54">
-        <v>-0.1853684800000004</v>
+        <v>-0.2102217200000004</v>
       </c>
       <c r="P54">
-        <v>-1.668316320000003</v>
+        <v>-1.891995480000003</v>
       </c>
       <c r="Q54">
-        <v>7.261683679999996</v>
+        <v>7.038004519999996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1031239766692581</v>
+        <v>0.1043436357473274</v>
       </c>
       <c r="T54">
-        <v>0.8867836878641981</v>
+        <v>0.9056514259038618</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.08565668515840001</v>
+        <v>0.08404052128748679</v>
       </c>
       <c r="W54">
-        <v>0.1342255986187469</v>
+        <v>0.134462851474997</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.856566851584</v>
+        <v>0.8404052128748679</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1203068200829923</v>
+        <v>0.1213168200829923</v>
       </c>
       <c r="C55">
-        <v>-9.029887506556264</v>
+        <v>-11.76620586058493</v>
       </c>
       <c r="D55">
-        <v>80.55511249344374</v>
+        <v>79.51179413941507</v>
       </c>
       <c r="E55">
-        <v>37.82900000000001</v>
+        <v>39.52200000000001</v>
       </c>
       <c r="F55">
-        <v>89.72900000000001</v>
+        <v>91.42200000000001</v>
       </c>
       <c r="G55">
         <v>0.144</v>
@@ -5791,37 +5791,37 @@
         <v>11.07</v>
       </c>
       <c r="M55">
-        <v>13.1722172</v>
+        <v>13.4207496</v>
       </c>
       <c r="N55">
-        <v>-2.102217200000004</v>
+        <v>-2.350749600000002</v>
       </c>
       <c r="O55">
-        <v>-0.2102217200000004</v>
+        <v>-0.2350749600000002</v>
       </c>
       <c r="P55">
-        <v>-1.891995480000003</v>
+        <v>-2.115674640000002</v>
       </c>
       <c r="Q55">
-        <v>7.038004519999996</v>
+        <v>6.814325359999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1043436357473274</v>
+        <v>0.105616323480965</v>
       </c>
       <c r="T55">
-        <v>0.9056514259038618</v>
+        <v>0.9253395003800329</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.08404052128748679</v>
+        <v>0.08248421533771853</v>
       </c>
       <c r="W55">
-        <v>0.134462851474997</v>
+        <v>0.1346913171884229</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8404052128748679</v>
+        <v>0.8248421533771852</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1213168200829923</v>
+        <v>0.1223268200829923</v>
       </c>
       <c r="C56">
-        <v>-11.76620586058493</v>
+        <v>-14.47584445676658</v>
       </c>
       <c r="D56">
-        <v>79.51179413941507</v>
+        <v>78.49515554323342</v>
       </c>
       <c r="E56">
-        <v>39.52200000000001</v>
+        <v>41.21500000000001</v>
       </c>
       <c r="F56">
-        <v>91.42200000000001</v>
+        <v>93.11500000000001</v>
       </c>
       <c r="G56">
         <v>0.144</v>
@@ -5873,37 +5873,37 @@
         <v>11.07</v>
       </c>
       <c r="M56">
-        <v>13.4207496</v>
+        <v>13.669282</v>
       </c>
       <c r="N56">
-        <v>-2.350749600000002</v>
+        <v>-2.599282000000002</v>
       </c>
       <c r="O56">
-        <v>-0.2350749600000002</v>
+        <v>-0.2599282000000002</v>
       </c>
       <c r="P56">
-        <v>-2.115674640000002</v>
+        <v>-2.339353800000002</v>
       </c>
       <c r="Q56">
-        <v>6.814325359999998</v>
+        <v>6.590646199999997</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.105616323480965</v>
+        <v>0.1069455751138753</v>
       </c>
       <c r="T56">
-        <v>0.9253395003800329</v>
+        <v>0.945902600388478</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.08248421533771853</v>
+        <v>0.0809845023315782</v>
       </c>
       <c r="W56">
-        <v>0.1346913171884229</v>
+        <v>0.1349114750577243</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8248421533771852</v>
+        <v>0.8098450233157819</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1223268200829923</v>
+        <v>0.1539217734333089</v>
       </c>
       <c r="C57">
-        <v>-14.47584445676658</v>
+        <v>-38.59497659300749</v>
       </c>
       <c r="D57">
-        <v>78.49515554323342</v>
+        <v>56.06902340699253</v>
       </c>
       <c r="E57">
-        <v>41.21500000000001</v>
+        <v>42.90800000000002</v>
       </c>
       <c r="F57">
-        <v>93.11500000000001</v>
+        <v>94.80800000000002</v>
       </c>
       <c r="G57">
         <v>0.144</v>
@@ -5955,45 +5955,45 @@
         <v>11.07</v>
       </c>
       <c r="M57">
-        <v>13.669282</v>
+        <v>19.0374464</v>
       </c>
       <c r="N57">
-        <v>-2.599282000000002</v>
+        <v>-7.967446400000004</v>
       </c>
       <c r="O57">
-        <v>-0.2599282000000002</v>
+        <v>-0.7967446400000004</v>
       </c>
       <c r="P57">
-        <v>-2.339353800000002</v>
+        <v>-7.170701760000004</v>
       </c>
       <c r="Q57">
-        <v>6.590646199999997</v>
+        <v>1.759298239999996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1069455751138753</v>
+        <v>0.1091192321626375</v>
       </c>
       <c r="T57">
-        <v>0.945902600388478</v>
+        <v>0.9795283836270481</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.0809845023315782</v>
+        <v>0.05814855504990416</v>
       </c>
       <c r="W57">
-        <v>0.1349114750577243</v>
+        <v>0.1891237701459793</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8098450233157819</v>
+        <v>0.5814855504990416</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1539217734333089</v>
+        <v>0.1554717734333089</v>
       </c>
       <c r="C58">
-        <v>-38.59497659300749</v>
+        <v>-41.06298009784972</v>
       </c>
       <c r="D58">
-        <v>56.06902340699253</v>
+        <v>55.2940199021503</v>
       </c>
       <c r="E58">
-        <v>42.90800000000002</v>
+        <v>44.60100000000002</v>
       </c>
       <c r="F58">
-        <v>94.80800000000002</v>
+        <v>96.50100000000002</v>
       </c>
       <c r="G58">
         <v>0.144</v>
@@ -6037,37 +6037,37 @@
         <v>11.07</v>
       </c>
       <c r="M58">
-        <v>19.0374464</v>
+        <v>19.3774008</v>
       </c>
       <c r="N58">
-        <v>-7.967446400000004</v>
+        <v>-8.307400800000003</v>
       </c>
       <c r="O58">
-        <v>-0.7967446400000004</v>
+        <v>-0.8307400800000004</v>
       </c>
       <c r="P58">
-        <v>-7.170701760000004</v>
+        <v>-7.476660720000003</v>
       </c>
       <c r="Q58">
-        <v>1.759298239999996</v>
+        <v>1.453339279999996</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1091192321626375</v>
+        <v>0.1105917724454895</v>
       </c>
       <c r="T58">
-        <v>0.9795283836270481</v>
+        <v>1.00230811347884</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.05814855504990416</v>
+        <v>0.05712840496130936</v>
       </c>
       <c r="W58">
-        <v>0.1891237701459793</v>
+        <v>0.1893286162837691</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5814855504990416</v>
+        <v>0.5712840496130935</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1554717734333089</v>
+        <v>0.1570217734333089</v>
       </c>
       <c r="C59">
-        <v>-41.06298009784972</v>
+        <v>-43.50985102412044</v>
       </c>
       <c r="D59">
-        <v>55.2940199021503</v>
+        <v>54.54014897587957</v>
       </c>
       <c r="E59">
-        <v>44.60100000000002</v>
+        <v>46.29400000000002</v>
       </c>
       <c r="F59">
-        <v>96.50100000000002</v>
+        <v>98.19400000000002</v>
       </c>
       <c r="G59">
         <v>0.144</v>
@@ -6119,37 +6119,37 @@
         <v>11.07</v>
       </c>
       <c r="M59">
-        <v>19.3774008</v>
+        <v>19.7173552</v>
       </c>
       <c r="N59">
-        <v>-8.307400800000003</v>
+        <v>-8.647355200000003</v>
       </c>
       <c r="O59">
-        <v>-0.8307400800000004</v>
+        <v>-0.8647355200000004</v>
       </c>
       <c r="P59">
-        <v>-7.476660720000003</v>
+        <v>-7.782619680000003</v>
       </c>
       <c r="Q59">
-        <v>1.453339279999996</v>
+        <v>1.147380319999996</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1105917724454895</v>
+        <v>0.1121344336941916</v>
       </c>
       <c r="T59">
-        <v>1.00230811347884</v>
+        <v>1.026172592371193</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.05712840496130936</v>
+        <v>0.05614343246197643</v>
       </c>
       <c r="W59">
-        <v>0.1893286162837691</v>
+        <v>0.1895263987616352</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5712840496130935</v>
+        <v>0.5614343246197644</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1570217734333089</v>
+        <v>0.1585717734333089</v>
       </c>
       <c r="C60">
-        <v>-43.50985102412043</v>
+        <v>-45.93644210167335</v>
       </c>
       <c r="D60">
-        <v>54.54014897587957</v>
+        <v>53.80655789832665</v>
       </c>
       <c r="E60">
-        <v>46.294</v>
+        <v>47.987</v>
       </c>
       <c r="F60">
-        <v>98.194</v>
+        <v>99.887</v>
       </c>
       <c r="G60">
         <v>0.144</v>
@@ -6201,37 +6201,37 @@
         <v>11.07</v>
       </c>
       <c r="M60">
-        <v>19.7173552</v>
+        <v>20.0573096</v>
       </c>
       <c r="N60">
-        <v>-8.6473552</v>
+        <v>-8.9873096</v>
       </c>
       <c r="O60">
-        <v>-0.86473552</v>
+        <v>-0.89873096</v>
       </c>
       <c r="P60">
-        <v>-7.78261968</v>
+        <v>-8.08857864</v>
       </c>
       <c r="Q60">
-        <v>1.14738032</v>
+        <v>0.84142136</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1121344336941916</v>
+        <v>0.1137523467111231</v>
       </c>
       <c r="T60">
-        <v>1.026172592371193</v>
+        <v>1.051201192185125</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05614343246197644</v>
+        <v>0.055191848860926</v>
       </c>
       <c r="W60">
-        <v>0.1895263987616352</v>
+        <v>0.1897174767487261</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5614343246197644</v>
+        <v>0.55191848860926</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1585717734333089</v>
+        <v>0.1601217734333089</v>
       </c>
       <c r="C61">
-        <v>-45.93644210167335</v>
+        <v>-48.34356079076314</v>
       </c>
       <c r="D61">
-        <v>53.80655789832665</v>
+        <v>53.09243920923686</v>
       </c>
       <c r="E61">
-        <v>47.987</v>
+        <v>49.68</v>
       </c>
       <c r="F61">
-        <v>99.887</v>
+        <v>101.58</v>
       </c>
       <c r="G61">
         <v>0.144</v>
@@ -6283,37 +6283,37 @@
         <v>11.07</v>
       </c>
       <c r="M61">
-        <v>20.0573096</v>
+        <v>20.397264</v>
       </c>
       <c r="N61">
-        <v>-8.9873096</v>
+        <v>-9.327264</v>
       </c>
       <c r="O61">
-        <v>-0.89873096</v>
+        <v>-0.9327264</v>
       </c>
       <c r="P61">
-        <v>-8.08857864</v>
+        <v>-8.3945376</v>
       </c>
       <c r="Q61">
-        <v>0.84142136</v>
+        <v>0.5354624000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1137523467111231</v>
+        <v>0.1154511553789012</v>
       </c>
       <c r="T61">
-        <v>1.051201192185125</v>
+        <v>1.077481221989753</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.055191848860926</v>
+        <v>0.0542719847132439</v>
       </c>
       <c r="W61">
-        <v>0.1897174767487261</v>
+        <v>0.1899021854695806</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.55191848860926</v>
+        <v>0.542719847132439</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1601217734333089</v>
+        <v>0.1616717734333089</v>
       </c>
       <c r="C62">
-        <v>-48.34356079076314</v>
+        <v>-50.73197224678</v>
       </c>
       <c r="D62">
-        <v>53.09243920923686</v>
+        <v>52.39702775322001</v>
       </c>
       <c r="E62">
-        <v>49.68</v>
+        <v>51.37300000000001</v>
       </c>
       <c r="F62">
-        <v>101.58</v>
+        <v>103.273</v>
       </c>
       <c r="G62">
         <v>0.144</v>
@@ -6365,37 +6365,37 @@
         <v>11.07</v>
       </c>
       <c r="M62">
-        <v>20.397264</v>
+        <v>20.7372184</v>
       </c>
       <c r="N62">
-        <v>-9.327264</v>
+        <v>-9.667218400000003</v>
       </c>
       <c r="O62">
-        <v>-0.9327264</v>
+        <v>-0.9667218400000004</v>
       </c>
       <c r="P62">
-        <v>-8.3945376</v>
+        <v>-8.700496560000003</v>
       </c>
       <c r="Q62">
-        <v>0.5354624000000001</v>
+        <v>0.2295034399999967</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1154511553789012</v>
+        <v>0.1172370824398987</v>
       </c>
       <c r="T62">
-        <v>1.077481221989753</v>
+        <v>1.105108945630516</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.0542719847132439</v>
+        <v>0.05338228004581366</v>
       </c>
       <c r="W62">
-        <v>0.1899021854695806</v>
+        <v>0.1900808381668006</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.542719847132439</v>
+        <v>0.5338228004581366</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1616717734333089</v>
+        <v>0.1632217734333088</v>
       </c>
       <c r="C63">
-        <v>-50.73197224678</v>
+        <v>-53.10240205500174</v>
       </c>
       <c r="D63">
-        <v>52.39702775322001</v>
+        <v>51.71959794499827</v>
       </c>
       <c r="E63">
-        <v>51.37300000000001</v>
+        <v>53.06600000000001</v>
       </c>
       <c r="F63">
-        <v>103.273</v>
+        <v>104.966</v>
       </c>
       <c r="G63">
         <v>0.144</v>
@@ -6447,37 +6447,37 @@
         <v>11.07</v>
       </c>
       <c r="M63">
-        <v>20.7372184</v>
+        <v>21.0771728</v>
       </c>
       <c r="N63">
-        <v>-9.667218400000003</v>
+        <v>-10.0071728</v>
       </c>
       <c r="O63">
-        <v>-0.9667218400000004</v>
+        <v>-1.00071728</v>
       </c>
       <c r="P63">
-        <v>-8.700496560000003</v>
+        <v>-9.006455520000003</v>
       </c>
       <c r="Q63">
-        <v>0.2295034399999967</v>
+        <v>-0.07645552000000322</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1172370824398987</v>
+        <v>0.1191170056620013</v>
       </c>
       <c r="T63">
-        <v>1.105108945630516</v>
+        <v>1.134190759989214</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05338228004581366</v>
+        <v>0.0525212755289457</v>
       </c>
       <c r="W63">
-        <v>0.1900808381668006</v>
+        <v>0.1902537278737877</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5338228004581366</v>
+        <v>0.525212755289457</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1632217734333088</v>
+        <v>0.1647717734333088</v>
       </c>
       <c r="C64">
-        <v>-53.10240205500174</v>
+        <v>-55.45553875591152</v>
       </c>
       <c r="D64">
-        <v>51.71959794499827</v>
+        <v>51.05946124408849</v>
       </c>
       <c r="E64">
-        <v>53.06600000000001</v>
+        <v>54.75900000000001</v>
       </c>
       <c r="F64">
-        <v>104.966</v>
+        <v>106.659</v>
       </c>
       <c r="G64">
         <v>0.144</v>
@@ -6529,37 +6529,37 @@
         <v>11.07</v>
       </c>
       <c r="M64">
-        <v>21.0771728</v>
+        <v>21.4171272</v>
       </c>
       <c r="N64">
-        <v>-10.0071728</v>
+        <v>-10.3471272</v>
       </c>
       <c r="O64">
-        <v>-1.00071728</v>
+        <v>-1.03471272</v>
       </c>
       <c r="P64">
-        <v>-9.006455520000003</v>
+        <v>-9.312414480000003</v>
       </c>
       <c r="Q64">
-        <v>-0.07645552000000322</v>
+        <v>-0.3824144800000031</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1191170056620013</v>
+        <v>0.1210985463555689</v>
       </c>
       <c r="T64">
-        <v>1.134190759989214</v>
+        <v>1.164844564313246</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.0525212755289457</v>
+        <v>0.05168760448880371</v>
       </c>
       <c r="W64">
-        <v>0.1902537278737877</v>
+        <v>0.1904211290186482</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.525212755289457</v>
+        <v>0.516876044888037</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1647717734333088</v>
+        <v>0.1663217734333089</v>
       </c>
       <c r="C65">
-        <v>-55.45553875591152</v>
+        <v>-57.79203617955751</v>
       </c>
       <c r="D65">
-        <v>51.05946124408849</v>
+        <v>50.4159638204425</v>
       </c>
       <c r="E65">
-        <v>54.75900000000001</v>
+        <v>56.45200000000001</v>
       </c>
       <c r="F65">
-        <v>106.659</v>
+        <v>108.352</v>
       </c>
       <c r="G65">
         <v>0.144</v>
@@ -6611,37 +6611,37 @@
         <v>11.07</v>
       </c>
       <c r="M65">
-        <v>21.4171272</v>
+        <v>21.7570816</v>
       </c>
       <c r="N65">
-        <v>-10.3471272</v>
+        <v>-10.6870816</v>
       </c>
       <c r="O65">
-        <v>-1.03471272</v>
+        <v>-1.06870816</v>
       </c>
       <c r="P65">
-        <v>-9.312414480000003</v>
+        <v>-9.618373440000003</v>
       </c>
       <c r="Q65">
-        <v>-0.3824144800000031</v>
+        <v>-0.688373440000003</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1210985463555689</v>
+        <v>0.1231901726432236</v>
       </c>
       <c r="T65">
-        <v>1.164844564313246</v>
+        <v>1.197201357766392</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05168760448880371</v>
+        <v>0.05087998566866615</v>
       </c>
       <c r="W65">
-        <v>0.1904211290186482</v>
+        <v>0.1905832988777318</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.516876044888037</v>
+        <v>0.5087998566866614</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1663217734333089</v>
+        <v>0.1678717734333089</v>
       </c>
       <c r="C66">
-        <v>-57.79203617955751</v>
+        <v>-60.11251560559143</v>
       </c>
       <c r="D66">
-        <v>50.4159638204425</v>
+        <v>49.78848439440858</v>
       </c>
       <c r="E66">
-        <v>56.45200000000001</v>
+        <v>58.14500000000002</v>
       </c>
       <c r="F66">
-        <v>108.352</v>
+        <v>110.045</v>
       </c>
       <c r="G66">
         <v>0.144</v>
@@ -6693,37 +6693,37 @@
         <v>11.07</v>
       </c>
       <c r="M66">
-        <v>21.7570816</v>
+        <v>22.097036</v>
       </c>
       <c r="N66">
-        <v>-10.6870816</v>
+        <v>-11.027036</v>
       </c>
       <c r="O66">
-        <v>-1.06870816</v>
+        <v>-1.1027036</v>
       </c>
       <c r="P66">
-        <v>-9.618373440000003</v>
+        <v>-9.924332400000003</v>
       </c>
       <c r="Q66">
-        <v>-0.688373440000003</v>
+        <v>-0.9943324000000029</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1231901726432236</v>
+        <v>0.12540132043303</v>
       </c>
       <c r="T66">
-        <v>1.197201357766392</v>
+        <v>1.231407110845432</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05087998566866615</v>
+        <v>0.05009721665837898</v>
       </c>
       <c r="W66">
-        <v>0.1905832988777318</v>
+        <v>0.1907404788949975</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5087998566866614</v>
+        <v>0.5009721665837897</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1678717734333089</v>
+        <v>0.192660966276736</v>
       </c>
       <c r="C67">
-        <v>-60.11251560559143</v>
+        <v>-70.07072251215682</v>
       </c>
       <c r="D67">
-        <v>49.78848439440858</v>
+        <v>41.5232774878432</v>
       </c>
       <c r="E67">
-        <v>58.14500000000002</v>
+        <v>59.83800000000002</v>
       </c>
       <c r="F67">
-        <v>110.045</v>
+        <v>111.738</v>
       </c>
       <c r="G67">
         <v>0.144</v>
@@ -6775,45 +6775,45 @@
         <v>11.07</v>
       </c>
       <c r="M67">
-        <v>22.097036</v>
+        <v>26.3478204</v>
       </c>
       <c r="N67">
-        <v>-11.027036</v>
+        <v>-15.2778204</v>
       </c>
       <c r="O67">
-        <v>-1.1027036</v>
+        <v>-1.52778204</v>
       </c>
       <c r="P67">
-        <v>-9.924332400000003</v>
+        <v>-13.75003836</v>
       </c>
       <c r="Q67">
-        <v>-0.9943324000000029</v>
+        <v>-4.820038360000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.12540132043303</v>
+        <v>0.128151926455846</v>
       </c>
       <c r="T67">
-        <v>1.231407110845432</v>
+        <v>1.273958111220854</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05009721665837898</v>
+        <v>0.04201486055370257</v>
       </c>
       <c r="W67">
-        <v>0.1907404788949975</v>
+        <v>0.225892895881437</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5009721665837897</v>
+        <v>0.4201486055370257</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.192660966276736</v>
+        <v>0.194560966276736</v>
       </c>
       <c r="C68">
-        <v>-70.07072251215682</v>
+        <v>-72.28541749231968</v>
       </c>
       <c r="D68">
-        <v>41.5232774878432</v>
+        <v>41.00158250768033</v>
       </c>
       <c r="E68">
-        <v>59.83800000000002</v>
+        <v>61.53100000000001</v>
       </c>
       <c r="F68">
-        <v>111.738</v>
+        <v>113.431</v>
       </c>
       <c r="G68">
         <v>0.144</v>
@@ -6857,37 +6857,37 @@
         <v>11.07</v>
       </c>
       <c r="M68">
-        <v>26.3478204</v>
+        <v>26.7470298</v>
       </c>
       <c r="N68">
-        <v>-15.2778204</v>
+        <v>-15.6770298</v>
       </c>
       <c r="O68">
-        <v>-1.52778204</v>
+        <v>-1.56770298</v>
       </c>
       <c r="P68">
-        <v>-13.75003836</v>
+        <v>-14.10932682</v>
       </c>
       <c r="Q68">
-        <v>-4.820038360000003</v>
+        <v>-5.179326820000004</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.128151926455846</v>
+        <v>0.1306474393787504</v>
       </c>
       <c r="T68">
-        <v>1.273958111220854</v>
+        <v>1.312562902469971</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04201486055370257</v>
+        <v>0.04138777308275179</v>
       </c>
       <c r="W68">
-        <v>0.225892895881437</v>
+        <v>0.2260407631070872</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4201486055370257</v>
+        <v>0.4138777308275179</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.194560966276736</v>
+        <v>0.196460966276736</v>
       </c>
       <c r="C69">
-        <v>-72.28541749231968</v>
+        <v>-74.48716606598725</v>
       </c>
       <c r="D69">
-        <v>41.00158250768033</v>
+        <v>40.49283393401275</v>
       </c>
       <c r="E69">
-        <v>61.53100000000001</v>
+        <v>63.22400000000001</v>
       </c>
       <c r="F69">
-        <v>113.431</v>
+        <v>115.124</v>
       </c>
       <c r="G69">
         <v>0.144</v>
@@ -6939,37 +6939,37 @@
         <v>11.07</v>
       </c>
       <c r="M69">
-        <v>26.7470298</v>
+        <v>27.1462392</v>
       </c>
       <c r="N69">
-        <v>-15.6770298</v>
+        <v>-16.0762392</v>
       </c>
       <c r="O69">
-        <v>-1.56770298</v>
+        <v>-1.60762392</v>
       </c>
       <c r="P69">
-        <v>-14.10932682</v>
+        <v>-14.46861528</v>
       </c>
       <c r="Q69">
-        <v>-5.179326820000004</v>
+        <v>-5.538615280000004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1306474393787504</v>
+        <v>0.1332989218593364</v>
       </c>
       <c r="T69">
-        <v>1.312562902469971</v>
+        <v>1.353580493172158</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04138777308275179</v>
+        <v>0.04077912936094662</v>
       </c>
       <c r="W69">
-        <v>0.2260407631070872</v>
+        <v>0.2261842812966888</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4138777308275179</v>
+        <v>0.4077912936094661</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.196460966276736</v>
+        <v>0.1983609662767361</v>
       </c>
       <c r="C70">
-        <v>-74.48716606598725</v>
+        <v>-76.67644424472104</v>
       </c>
       <c r="D70">
-        <v>40.49283393401275</v>
+        <v>39.99655575527899</v>
       </c>
       <c r="E70">
-        <v>63.22400000000001</v>
+        <v>64.91700000000003</v>
       </c>
       <c r="F70">
-        <v>115.124</v>
+        <v>116.817</v>
       </c>
       <c r="G70">
         <v>0.144</v>
@@ -7021,37 +7021,37 @@
         <v>11.07</v>
       </c>
       <c r="M70">
-        <v>27.1462392</v>
+        <v>27.54544860000001</v>
       </c>
       <c r="N70">
-        <v>-16.0762392</v>
+        <v>-16.47544860000001</v>
       </c>
       <c r="O70">
-        <v>-1.60762392</v>
+        <v>-1.647544860000001</v>
       </c>
       <c r="P70">
-        <v>-14.46861528</v>
+        <v>-14.82790374000001</v>
       </c>
       <c r="Q70">
-        <v>-5.538615280000004</v>
+        <v>-5.897903740000007</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1332989218593364</v>
+        <v>0.1361214677257666</v>
       </c>
       <c r="T70">
-        <v>1.353580493172158</v>
+        <v>1.397244380048679</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04077912936094662</v>
+        <v>0.04018812748615028</v>
       </c>
       <c r="W70">
-        <v>0.2261842812966888</v>
+        <v>0.2263236395387658</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4077912936094661</v>
+        <v>0.4018812748615028</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1983609662767361</v>
+        <v>0.200260966276736</v>
       </c>
       <c r="C71">
-        <v>-76.67644424472104</v>
+        <v>-78.85370498672624</v>
       </c>
       <c r="D71">
-        <v>39.99655575527899</v>
+        <v>39.51229501327378</v>
       </c>
       <c r="E71">
-        <v>64.91700000000003</v>
+        <v>66.61000000000001</v>
       </c>
       <c r="F71">
-        <v>116.817</v>
+        <v>118.51</v>
       </c>
       <c r="G71">
         <v>0.144</v>
@@ -7103,37 +7103,37 @@
         <v>11.07</v>
       </c>
       <c r="M71">
-        <v>27.54544860000001</v>
+        <v>27.944658</v>
       </c>
       <c r="N71">
-        <v>-16.47544860000001</v>
+        <v>-16.874658</v>
       </c>
       <c r="O71">
-        <v>-1.647544860000001</v>
+        <v>-1.6874658</v>
       </c>
       <c r="P71">
-        <v>-14.82790374000001</v>
+        <v>-15.1871922</v>
       </c>
       <c r="Q71">
-        <v>-5.897903740000007</v>
+        <v>-6.257192200000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1361214677257666</v>
+        <v>0.1391321833166255</v>
       </c>
       <c r="T71">
-        <v>1.397244380048679</v>
+        <v>1.443819192716968</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04018812748615028</v>
+        <v>0.03961401137920528</v>
       </c>
       <c r="W71">
-        <v>0.2263236395387658</v>
+        <v>0.2264590161167834</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4018812748615028</v>
+        <v>0.3961401137920528</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.200260966276736</v>
+        <v>0.202160966276736</v>
       </c>
       <c r="C72">
-        <v>-78.85370498672624</v>
+        <v>-81.01937957575635</v>
       </c>
       <c r="D72">
-        <v>39.51229501327378</v>
+        <v>39.03962042424367</v>
       </c>
       <c r="E72">
-        <v>66.61000000000001</v>
+        <v>68.30300000000003</v>
       </c>
       <c r="F72">
-        <v>118.51</v>
+        <v>120.203</v>
       </c>
       <c r="G72">
         <v>0.144</v>
@@ -7185,37 +7185,37 @@
         <v>11.07</v>
       </c>
       <c r="M72">
-        <v>27.944658</v>
+        <v>28.3438674</v>
       </c>
       <c r="N72">
-        <v>-16.874658</v>
+        <v>-17.2738674</v>
       </c>
       <c r="O72">
-        <v>-1.6874658</v>
+        <v>-1.72738674</v>
       </c>
       <c r="P72">
-        <v>-15.1871922</v>
+        <v>-15.54648066</v>
       </c>
       <c r="Q72">
-        <v>-6.257192200000004</v>
+        <v>-6.616480660000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1391321833166255</v>
+        <v>0.1423505344654746</v>
       </c>
       <c r="T72">
-        <v>1.443819192716968</v>
+        <v>1.493606061431346</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03961401137920528</v>
+        <v>0.03905606755696295</v>
       </c>
       <c r="W72">
-        <v>0.2264590161167834</v>
+        <v>0.2265905792700681</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3961401137920528</v>
+        <v>0.3905606755696295</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.202160966276736</v>
+        <v>0.204060966276736</v>
       </c>
       <c r="C73">
-        <v>-81.01937957575632</v>
+        <v>-83.17387890221465</v>
       </c>
       <c r="D73">
-        <v>39.03962042424369</v>
+        <v>38.57812109778535</v>
       </c>
       <c r="E73">
-        <v>68.303</v>
+        <v>69.99600000000001</v>
       </c>
       <c r="F73">
-        <v>120.203</v>
+        <v>121.896</v>
       </c>
       <c r="G73">
         <v>0.144</v>
@@ -7267,37 +7267,37 @@
         <v>11.07</v>
       </c>
       <c r="M73">
-        <v>28.3438674</v>
+        <v>28.7430768</v>
       </c>
       <c r="N73">
-        <v>-17.2738674</v>
+        <v>-17.6730768</v>
       </c>
       <c r="O73">
-        <v>-1.72738674</v>
+        <v>-1.76730768</v>
       </c>
       <c r="P73">
-        <v>-15.54648066</v>
+        <v>-15.90576912</v>
       </c>
       <c r="Q73">
-        <v>-6.616480660000001</v>
+        <v>-6.975769120000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1423505344654746</v>
+        <v>0.1457987678392416</v>
       </c>
       <c r="T73">
-        <v>1.493606061431346</v>
+        <v>1.546949135053894</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03905606755696296</v>
+        <v>0.03851362217422736</v>
       </c>
       <c r="W73">
-        <v>0.2265905792700681</v>
+        <v>0.2267184878913172</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3905606755696296</v>
+        <v>0.3851362217422736</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.204060966276736</v>
+        <v>0.205960966276736</v>
       </c>
       <c r="C74">
-        <v>-83.17387890221465</v>
+        <v>-85.31759465445202</v>
       </c>
       <c r="D74">
-        <v>38.57812109778535</v>
+        <v>38.12740534554798</v>
       </c>
       <c r="E74">
-        <v>69.99600000000001</v>
+        <v>71.68899999999999</v>
       </c>
       <c r="F74">
-        <v>121.896</v>
+        <v>123.589</v>
       </c>
       <c r="G74">
         <v>0.144</v>
@@ -7349,37 +7349,37 @@
         <v>11.07</v>
       </c>
       <c r="M74">
-        <v>28.7430768</v>
+        <v>29.1422862</v>
       </c>
       <c r="N74">
-        <v>-17.6730768</v>
+        <v>-18.0722862</v>
       </c>
       <c r="O74">
-        <v>-1.76730768</v>
+        <v>-1.80722862</v>
       </c>
       <c r="P74">
-        <v>-15.90576912</v>
+        <v>-16.26505758</v>
       </c>
       <c r="Q74">
-        <v>-6.975769120000001</v>
+        <v>-7.335057580000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1457987678392416</v>
+        <v>0.1495024259073616</v>
       </c>
       <c r="T74">
-        <v>1.546949135053894</v>
+        <v>1.604243547463297</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03851362217422736</v>
+        <v>0.03798603830882699</v>
       </c>
       <c r="W74">
-        <v>0.2267184878913172</v>
+        <v>0.2268428921667786</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3851362217422736</v>
+        <v>0.3798603830882699</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.205960966276736</v>
+        <v>0.207860966276736</v>
       </c>
       <c r="C75">
-        <v>-85.31759465445202</v>
+        <v>-87.45090042751963</v>
       </c>
       <c r="D75">
-        <v>38.12740534554798</v>
+        <v>37.68709957248038</v>
       </c>
       <c r="E75">
-        <v>71.68899999999999</v>
+        <v>73.38200000000001</v>
       </c>
       <c r="F75">
-        <v>123.589</v>
+        <v>125.282</v>
       </c>
       <c r="G75">
         <v>0.144</v>
@@ -7431,37 +7431,37 @@
         <v>11.07</v>
       </c>
       <c r="M75">
-        <v>29.1422862</v>
+        <v>29.5414956</v>
       </c>
       <c r="N75">
-        <v>-18.0722862</v>
+        <v>-18.4714956</v>
       </c>
       <c r="O75">
-        <v>-1.80722862</v>
+        <v>-1.847149560000001</v>
       </c>
       <c r="P75">
-        <v>-16.26505758</v>
+        <v>-16.62434604</v>
       </c>
       <c r="Q75">
-        <v>-7.335057580000001</v>
+        <v>-7.694346040000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1495024259073616</v>
+        <v>0.1534909807499525</v>
       </c>
       <c r="T75">
-        <v>1.604243547463297</v>
+        <v>1.665945222365732</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03798603830882699</v>
+        <v>0.03747271346681581</v>
       </c>
       <c r="W75">
-        <v>0.2268428921667786</v>
+        <v>0.2269639341645248</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3798603830882699</v>
+        <v>0.3747271346681581</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.207860966276736</v>
+        <v>0.209760966276736</v>
       </c>
       <c r="C76">
-        <v>-87.45090042751963</v>
+        <v>-89.5741527559739</v>
       </c>
       <c r="D76">
-        <v>37.68709957248038</v>
+        <v>37.25684724402612</v>
       </c>
       <c r="E76">
-        <v>73.38200000000001</v>
+        <v>75.07500000000002</v>
       </c>
       <c r="F76">
-        <v>125.282</v>
+        <v>126.975</v>
       </c>
       <c r="G76">
         <v>0.144</v>
@@ -7513,37 +7513,37 @@
         <v>11.07</v>
       </c>
       <c r="M76">
-        <v>29.5414956</v>
+        <v>29.940705</v>
       </c>
       <c r="N76">
-        <v>-18.4714956</v>
+        <v>-18.870705</v>
       </c>
       <c r="O76">
-        <v>-1.847149560000001</v>
+        <v>-1.887070500000001</v>
       </c>
       <c r="P76">
-        <v>-16.62434604</v>
+        <v>-16.9836345</v>
       </c>
       <c r="Q76">
-        <v>-7.694346040000003</v>
+        <v>-8.053634500000005</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1534909807499525</v>
+        <v>0.1577986199799505</v>
       </c>
       <c r="T76">
-        <v>1.665945222365732</v>
+        <v>1.732583031260361</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03747271346681581</v>
+        <v>0.03697307728725826</v>
       </c>
       <c r="W76">
-        <v>0.2269639341645248</v>
+        <v>0.2270817483756645</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3747271346681581</v>
+        <v>0.3697307728725826</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.209760966276736</v>
+        <v>0.211660966276736</v>
       </c>
       <c r="C77">
-        <v>-89.5741527559739</v>
+        <v>-91.68769207673438</v>
       </c>
       <c r="D77">
-        <v>37.25684724402612</v>
+        <v>36.83630792326562</v>
       </c>
       <c r="E77">
-        <v>75.07500000000002</v>
+        <v>76.768</v>
       </c>
       <c r="F77">
-        <v>126.975</v>
+        <v>128.668</v>
       </c>
       <c r="G77">
         <v>0.144</v>
@@ -7595,37 +7595,37 @@
         <v>11.07</v>
       </c>
       <c r="M77">
-        <v>29.940705</v>
+        <v>30.3399144</v>
       </c>
       <c r="N77">
-        <v>-18.870705</v>
+        <v>-19.2699144</v>
       </c>
       <c r="O77">
-        <v>-1.887070500000001</v>
+        <v>-1.92699144</v>
       </c>
       <c r="P77">
-        <v>-16.9836345</v>
+        <v>-17.34292296</v>
       </c>
       <c r="Q77">
-        <v>-8.053634500000005</v>
+        <v>-8.412922960000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1577986199799505</v>
+        <v>0.1624652291457819</v>
       </c>
       <c r="T77">
-        <v>1.732583031260361</v>
+        <v>1.80477399089621</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03697307728725826</v>
+        <v>0.03648658942821539</v>
       </c>
       <c r="W77">
-        <v>0.2270817483756645</v>
+        <v>0.2271964622128268</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3697307728725826</v>
+        <v>0.3648658942821539</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.211660966276736</v>
+        <v>0.213560966276736</v>
       </c>
       <c r="C78">
-        <v>-91.68769207673438</v>
+        <v>-93.7918436274593</v>
       </c>
       <c r="D78">
-        <v>36.83630792326562</v>
+        <v>36.42515637254072</v>
       </c>
       <c r="E78">
-        <v>76.768</v>
+        <v>78.46100000000001</v>
       </c>
       <c r="F78">
-        <v>128.668</v>
+        <v>130.361</v>
       </c>
       <c r="G78">
         <v>0.144</v>
@@ -7677,37 +7677,37 @@
         <v>11.07</v>
       </c>
       <c r="M78">
-        <v>30.3399144</v>
+        <v>30.73912380000001</v>
       </c>
       <c r="N78">
-        <v>-19.2699144</v>
+        <v>-19.6691238</v>
       </c>
       <c r="O78">
-        <v>-1.92699144</v>
+        <v>-1.966912380000001</v>
       </c>
       <c r="P78">
-        <v>-17.34292296</v>
+        <v>-17.70221142</v>
       </c>
       <c r="Q78">
-        <v>-8.412922960000003</v>
+        <v>-8.772211420000005</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1624652291457819</v>
+        <v>0.1675376304129897</v>
       </c>
       <c r="T78">
-        <v>1.80477399089621</v>
+        <v>1.883242425283002</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03648658942821539</v>
+        <v>0.03601273761745934</v>
       </c>
       <c r="W78">
-        <v>0.2271964622128268</v>
+        <v>0.2273081964698031</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3648658942821539</v>
+        <v>0.3601273761745934</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.213560966276736</v>
+        <v>0.215460966276736</v>
       </c>
       <c r="C79">
-        <v>-93.7918436274593</v>
+        <v>-95.88691828542156</v>
       </c>
       <c r="D79">
-        <v>36.42515637254072</v>
+        <v>36.02308171457845</v>
       </c>
       <c r="E79">
-        <v>78.46100000000001</v>
+        <v>80.154</v>
       </c>
       <c r="F79">
-        <v>130.361</v>
+        <v>132.054</v>
       </c>
       <c r="G79">
         <v>0.144</v>
@@ -7759,37 +7759,37 @@
         <v>11.07</v>
       </c>
       <c r="M79">
-        <v>30.73912380000001</v>
+        <v>31.1383332</v>
       </c>
       <c r="N79">
-        <v>-19.6691238</v>
+        <v>-20.0683332</v>
       </c>
       <c r="O79">
-        <v>-1.966912380000001</v>
+        <v>-2.00683332</v>
       </c>
       <c r="P79">
-        <v>-17.70221142</v>
+        <v>-18.06149988</v>
       </c>
       <c r="Q79">
-        <v>-8.772211420000005</v>
+        <v>-9.13149988</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1675376304129897</v>
+        <v>0.1730711590681256</v>
       </c>
       <c r="T79">
-        <v>1.883242425283002</v>
+        <v>1.968844353704956</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03601273761745934</v>
+        <v>0.03555103585313295</v>
       </c>
       <c r="W79">
-        <v>0.2273081964698031</v>
+        <v>0.2274170657458313</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3601273761745934</v>
+        <v>0.3555103585313295</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.215460966276736</v>
+        <v>0.217360966276736</v>
       </c>
       <c r="C80">
-        <v>-95.88691828542156</v>
+        <v>-97.97321335143232</v>
       </c>
       <c r="D80">
-        <v>36.02308171457845</v>
+        <v>35.6297866485677</v>
       </c>
       <c r="E80">
-        <v>80.154</v>
+        <v>81.84700000000001</v>
       </c>
       <c r="F80">
-        <v>132.054</v>
+        <v>133.747</v>
       </c>
       <c r="G80">
         <v>0.144</v>
@@ -7841,37 +7841,37 @@
         <v>11.07</v>
       </c>
       <c r="M80">
-        <v>31.1383332</v>
+        <v>31.53754260000001</v>
       </c>
       <c r="N80">
-        <v>-20.0683332</v>
+        <v>-20.46754260000001</v>
       </c>
       <c r="O80">
-        <v>-2.00683332</v>
+        <v>-2.046754260000001</v>
       </c>
       <c r="P80">
-        <v>-18.06149988</v>
+        <v>-18.42078834</v>
       </c>
       <c r="Q80">
-        <v>-9.13149988</v>
+        <v>-9.490788340000005</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1730711590681256</v>
+        <v>0.1791316904523221</v>
       </c>
       <c r="T80">
-        <v>1.968844353704956</v>
+        <v>2.062598846738526</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03555103585313295</v>
+        <v>0.03510102274106797</v>
       </c>
       <c r="W80">
-        <v>0.2274170657458313</v>
+        <v>0.2275231788376562</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3555103585313295</v>
+        <v>0.3510102274106797</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.217360966276736</v>
+        <v>0.219260966276736</v>
       </c>
       <c r="C81">
-        <v>-97.97321335143232</v>
+        <v>-100.0510132829666</v>
       </c>
       <c r="D81">
-        <v>35.6297866485677</v>
+        <v>35.24498671703338</v>
       </c>
       <c r="E81">
-        <v>81.84700000000001</v>
+        <v>83.54000000000002</v>
       </c>
       <c r="F81">
-        <v>133.747</v>
+        <v>135.44</v>
       </c>
       <c r="G81">
         <v>0.144</v>
@@ -7923,37 +7923,37 @@
         <v>11.07</v>
       </c>
       <c r="M81">
-        <v>31.53754260000001</v>
+        <v>31.93675200000001</v>
       </c>
       <c r="N81">
-        <v>-20.46754260000001</v>
+        <v>-20.86675200000001</v>
       </c>
       <c r="O81">
-        <v>-2.046754260000001</v>
+        <v>-2.086675200000001</v>
       </c>
       <c r="P81">
-        <v>-18.42078834</v>
+        <v>-18.78007680000001</v>
       </c>
       <c r="Q81">
-        <v>-9.490788340000005</v>
+        <v>-9.850076800000007</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1791316904523221</v>
+        <v>0.1857982749749382</v>
       </c>
       <c r="T81">
-        <v>2.062598846738526</v>
+        <v>2.165728789075452</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03510102274106797</v>
+        <v>0.03466225995680462</v>
       </c>
       <c r="W81">
-        <v>0.2275231788376562</v>
+        <v>0.2276266391021855</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3510102274106797</v>
+        <v>0.3466225995680462</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.219260966276736</v>
+        <v>0.2211609662767361</v>
       </c>
       <c r="C82">
-        <v>-100.0510132829666</v>
+        <v>-102.1205903802902</v>
       </c>
       <c r="D82">
-        <v>35.24498671703338</v>
+        <v>34.86840961970986</v>
       </c>
       <c r="E82">
-        <v>83.54000000000002</v>
+        <v>85.233</v>
       </c>
       <c r="F82">
-        <v>135.44</v>
+        <v>137.133</v>
       </c>
       <c r="G82">
         <v>0.144</v>
@@ -8005,37 +8005,37 @@
         <v>11.07</v>
       </c>
       <c r="M82">
-        <v>31.93675200000001</v>
+        <v>32.3359614</v>
       </c>
       <c r="N82">
-        <v>-20.86675200000001</v>
+        <v>-21.2659614</v>
       </c>
       <c r="O82">
-        <v>-2.086675200000001</v>
+        <v>-2.12659614</v>
       </c>
       <c r="P82">
-        <v>-18.78007680000001</v>
+        <v>-19.13936526</v>
       </c>
       <c r="Q82">
-        <v>-9.850076800000007</v>
+        <v>-10.20936526</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1857982749749382</v>
+        <v>0.1931666052367771</v>
       </c>
       <c r="T82">
-        <v>2.165728789075452</v>
+        <v>2.279714514816266</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03466225995680462</v>
+        <v>0.03423433082153543</v>
       </c>
       <c r="W82">
-        <v>0.2276266391021855</v>
+        <v>0.227727544792282</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3466225995680462</v>
+        <v>0.3423433082153543</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2211609662767361</v>
+        <v>0.2230609662767361</v>
       </c>
       <c r="C83">
-        <v>-102.1205903802902</v>
+        <v>-104.1822054290654</v>
       </c>
       <c r="D83">
-        <v>34.86840961970986</v>
+        <v>34.49979457093465</v>
       </c>
       <c r="E83">
-        <v>85.233</v>
+        <v>86.92600000000002</v>
       </c>
       <c r="F83">
-        <v>137.133</v>
+        <v>138.826</v>
       </c>
       <c r="G83">
         <v>0.144</v>
@@ -8087,37 +8087,37 @@
         <v>11.07</v>
       </c>
       <c r="M83">
-        <v>32.3359614</v>
+        <v>32.73517080000001</v>
       </c>
       <c r="N83">
-        <v>-21.2659614</v>
+        <v>-21.66517080000001</v>
       </c>
       <c r="O83">
-        <v>-2.12659614</v>
+        <v>-2.166517080000001</v>
       </c>
       <c r="P83">
-        <v>-19.13936526</v>
+        <v>-19.49865372</v>
       </c>
       <c r="Q83">
-        <v>-10.20936526</v>
+        <v>-10.56865372</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1931666052367771</v>
+        <v>0.2013536388610425</v>
       </c>
       <c r="T83">
-        <v>2.279714514816266</v>
+        <v>2.406365321194948</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03423433082153543</v>
+        <v>0.03381683898224841</v>
       </c>
       <c r="W83">
-        <v>0.227727544792282</v>
+        <v>0.2278259893679858</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3423433082153543</v>
+        <v>0.3381683898224841</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2230609662767361</v>
+        <v>0.2249609662767361</v>
       </c>
       <c r="C84">
-        <v>-104.1822054290654</v>
+        <v>-106.2361083026236</v>
       </c>
       <c r="D84">
-        <v>34.49979457093465</v>
+        <v>34.1388916973764</v>
       </c>
       <c r="E84">
-        <v>86.92600000000002</v>
+        <v>88.61900000000003</v>
       </c>
       <c r="F84">
-        <v>138.826</v>
+        <v>140.519</v>
       </c>
       <c r="G84">
         <v>0.144</v>
@@ -8169,37 +8169,37 @@
         <v>11.07</v>
       </c>
       <c r="M84">
-        <v>32.73517080000001</v>
+        <v>33.13438020000001</v>
       </c>
       <c r="N84">
-        <v>-21.66517080000001</v>
+        <v>-22.06438020000001</v>
       </c>
       <c r="O84">
-        <v>-2.166517080000001</v>
+        <v>-2.206438020000001</v>
       </c>
       <c r="P84">
-        <v>-19.49865372</v>
+        <v>-19.85794218000001</v>
       </c>
       <c r="Q84">
-        <v>-10.56865372</v>
+        <v>-10.92794218000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2013536388610425</v>
+        <v>0.210503852911692</v>
       </c>
       <c r="T84">
-        <v>2.406365321194948</v>
+        <v>2.547916222441709</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03381683898224841</v>
+        <v>0.03340940718728156</v>
       </c>
       <c r="W84">
-        <v>0.2278259893679858</v>
+        <v>0.227922061785239</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3381683898224841</v>
+        <v>0.3340940718728156</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2249609662767361</v>
+        <v>0.226860966276736</v>
       </c>
       <c r="C85">
-        <v>-106.2361083026236</v>
+        <v>-108.2825385268266</v>
       </c>
       <c r="D85">
-        <v>34.1388916973764</v>
+        <v>33.78546147317346</v>
       </c>
       <c r="E85">
-        <v>88.61900000000003</v>
+        <v>90.31200000000001</v>
       </c>
       <c r="F85">
-        <v>140.519</v>
+        <v>142.212</v>
       </c>
       <c r="G85">
         <v>0.144</v>
@@ -8251,37 +8251,37 @@
         <v>11.07</v>
       </c>
       <c r="M85">
-        <v>33.13438020000001</v>
+        <v>33.53358960000001</v>
       </c>
       <c r="N85">
-        <v>-22.06438020000001</v>
+        <v>-22.46358960000001</v>
       </c>
       <c r="O85">
-        <v>-2.206438020000001</v>
+        <v>-2.246358960000001</v>
       </c>
       <c r="P85">
-        <v>-19.85794218000001</v>
+        <v>-20.21723064</v>
       </c>
       <c r="Q85">
-        <v>-10.92794218000001</v>
+        <v>-11.28723064</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.210503852911692</v>
+        <v>0.2207978437186729</v>
       </c>
       <c r="T85">
-        <v>2.547916222441709</v>
+        <v>2.707160986344316</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03340940718728156</v>
+        <v>0.03301167614933773</v>
       </c>
       <c r="W85">
-        <v>0.227922061785239</v>
+        <v>0.2280158467639862</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3340940718728156</v>
+        <v>0.3301167614933773</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.226860966276736</v>
+        <v>0.228760966276736</v>
       </c>
       <c r="C86">
-        <v>-108.2825385268265</v>
+        <v>-110.3217258101996</v>
       </c>
       <c r="D86">
-        <v>33.78546147317348</v>
+        <v>33.43927418980036</v>
       </c>
       <c r="E86">
-        <v>90.31200000000001</v>
+        <v>92.005</v>
       </c>
       <c r="F86">
-        <v>142.212</v>
+        <v>143.905</v>
       </c>
       <c r="G86">
         <v>0.144</v>
@@ -8333,37 +8333,37 @@
         <v>11.07</v>
       </c>
       <c r="M86">
-        <v>33.53358960000001</v>
+        <v>33.932799</v>
       </c>
       <c r="N86">
-        <v>-22.46358960000001</v>
+        <v>-22.862799</v>
       </c>
       <c r="O86">
-        <v>-2.246358960000001</v>
+        <v>-2.2862799</v>
       </c>
       <c r="P86">
-        <v>-20.21723064</v>
+        <v>-20.5765191</v>
       </c>
       <c r="Q86">
-        <v>-11.28723064</v>
+        <v>-11.6465191</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2207978437186727</v>
+        <v>0.2324643666332509</v>
       </c>
       <c r="T86">
-        <v>2.707160986344314</v>
+        <v>2.887638385433936</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03301167614933773</v>
+        <v>0.0326233034887573</v>
       </c>
       <c r="W86">
-        <v>0.2280158467639862</v>
+        <v>0.228107425037351</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3301167614933773</v>
+        <v>0.3262330348875729</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.228760966276736</v>
+        <v>0.230660966276736</v>
       </c>
       <c r="C87">
-        <v>-110.3217258101996</v>
+        <v>-112.3538905418042</v>
       </c>
       <c r="D87">
-        <v>33.43927418980036</v>
+        <v>33.10010945819577</v>
       </c>
       <c r="E87">
-        <v>92.005</v>
+        <v>93.69800000000001</v>
       </c>
       <c r="F87">
-        <v>143.905</v>
+        <v>145.598</v>
       </c>
       <c r="G87">
         <v>0.144</v>
@@ -8415,37 +8415,37 @@
         <v>11.07</v>
       </c>
       <c r="M87">
-        <v>33.932799</v>
+        <v>34.33200840000001</v>
       </c>
       <c r="N87">
-        <v>-22.862799</v>
+        <v>-23.26200840000001</v>
       </c>
       <c r="O87">
-        <v>-2.2862799</v>
+        <v>-2.326200840000001</v>
       </c>
       <c r="P87">
-        <v>-20.5765191</v>
+        <v>-20.93580756</v>
       </c>
       <c r="Q87">
-        <v>-11.6465191</v>
+        <v>-12.00580756</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2324643666332509</v>
+        <v>0.2457975356784831</v>
       </c>
       <c r="T87">
-        <v>2.887638385433936</v>
+        <v>3.093898270107788</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0326233034887573</v>
+        <v>0.03224396275051593</v>
       </c>
       <c r="W87">
-        <v>0.228107425037351</v>
+        <v>0.2281968735834284</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3262330348875729</v>
+        <v>0.3224396275051592</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.230660966276736</v>
+        <v>0.232560966276736</v>
       </c>
       <c r="C88">
-        <v>-112.3538905418042</v>
+        <v>-114.3792442591146</v>
       </c>
       <c r="D88">
-        <v>33.10010945819577</v>
+        <v>32.76775574088536</v>
       </c>
       <c r="E88">
-        <v>93.69800000000001</v>
+        <v>95.39099999999999</v>
       </c>
       <c r="F88">
-        <v>145.598</v>
+        <v>147.291</v>
       </c>
       <c r="G88">
         <v>0.144</v>
@@ -8497,37 +8497,37 @@
         <v>11.07</v>
       </c>
       <c r="M88">
-        <v>34.33200840000001</v>
+        <v>34.7312178</v>
       </c>
       <c r="N88">
-        <v>-23.26200840000001</v>
+        <v>-23.6612178</v>
       </c>
       <c r="O88">
-        <v>-2.326200840000001</v>
+        <v>-2.36612178</v>
       </c>
       <c r="P88">
-        <v>-20.93580756</v>
+        <v>-21.29509602</v>
       </c>
       <c r="Q88">
-        <v>-12.00580756</v>
+        <v>-12.36509602</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2457975356784831</v>
+        <v>0.2611819614999049</v>
       </c>
       <c r="T88">
-        <v>3.093898270107788</v>
+        <v>3.331890444731464</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03224396275051593</v>
+        <v>0.03187334248901574</v>
       </c>
       <c r="W88">
-        <v>0.2281968735834284</v>
+        <v>0.2282842658410901</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3224396275051592</v>
+        <v>0.3187334248901574</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.232560966276736</v>
+        <v>0.234460966276736</v>
       </c>
       <c r="C89">
-        <v>-114.3792442591146</v>
+        <v>-116.3979900879886</v>
       </c>
       <c r="D89">
-        <v>32.76775574088536</v>
+        <v>32.44200991201142</v>
       </c>
       <c r="E89">
-        <v>95.39099999999999</v>
+        <v>97.084</v>
       </c>
       <c r="F89">
-        <v>147.291</v>
+        <v>148.984</v>
       </c>
       <c r="G89">
         <v>0.144</v>
@@ -8579,37 +8579,37 @@
         <v>11.07</v>
       </c>
       <c r="M89">
-        <v>34.7312178</v>
+        <v>35.13042720000001</v>
       </c>
       <c r="N89">
-        <v>-23.6612178</v>
+        <v>-24.06042720000001</v>
       </c>
       <c r="O89">
-        <v>-2.36612178</v>
+        <v>-2.406042720000001</v>
       </c>
       <c r="P89">
-        <v>-21.29509602</v>
+        <v>-21.65438448</v>
       </c>
       <c r="Q89">
-        <v>-12.36509602</v>
+        <v>-12.72438448</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2611819614999049</v>
+        <v>0.2791304582915637</v>
       </c>
       <c r="T89">
-        <v>3.331890444731464</v>
+        <v>3.609547981792421</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03187334248901574</v>
+        <v>0.03151114541527693</v>
       </c>
       <c r="W89">
-        <v>0.2282842658410901</v>
+        <v>0.2283696719110777</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3187334248901574</v>
+        <v>0.3151114541527693</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.234460966276736</v>
+        <v>0.236360966276736</v>
       </c>
       <c r="C90">
-        <v>-116.3979900879886</v>
+        <v>-118.4103231566531</v>
       </c>
       <c r="D90">
-        <v>32.44200991201142</v>
+        <v>32.12267684334693</v>
       </c>
       <c r="E90">
-        <v>97.084</v>
+        <v>98.77700000000002</v>
       </c>
       <c r="F90">
-        <v>148.984</v>
+        <v>150.677</v>
       </c>
       <c r="G90">
         <v>0.144</v>
@@ -8661,37 +8661,37 @@
         <v>11.07</v>
       </c>
       <c r="M90">
-        <v>35.13042720000001</v>
+        <v>35.5296366</v>
       </c>
       <c r="N90">
-        <v>-24.06042720000001</v>
+        <v>-24.4596366</v>
       </c>
       <c r="O90">
-        <v>-2.406042720000001</v>
+        <v>-2.44596366</v>
       </c>
       <c r="P90">
-        <v>-21.65438448</v>
+        <v>-22.01367294</v>
       </c>
       <c r="Q90">
-        <v>-12.72438448</v>
+        <v>-13.08367294</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2791304582915637</v>
+        <v>0.3003423181362513</v>
       </c>
       <c r="T90">
-        <v>3.609547981792421</v>
+        <v>3.937688707409913</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03151114541527693</v>
+        <v>0.03115708760162213</v>
       </c>
       <c r="W90">
-        <v>0.2283696719110777</v>
+        <v>0.2284531587435375</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3151114541527693</v>
+        <v>0.3115708760162214</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.236360966276736</v>
+        <v>0.238260966276736</v>
       </c>
       <c r="C91">
-        <v>-118.4103231566531</v>
+        <v>-120.4164309854791</v>
       </c>
       <c r="D91">
-        <v>32.12267684334693</v>
+        <v>31.80956901452091</v>
       </c>
       <c r="E91">
-        <v>98.77700000000002</v>
+        <v>100.47</v>
       </c>
       <c r="F91">
-        <v>150.677</v>
+        <v>152.37</v>
       </c>
       <c r="G91">
         <v>0.144</v>
@@ -8743,37 +8743,37 @@
         <v>11.07</v>
       </c>
       <c r="M91">
-        <v>35.5296366</v>
+        <v>35.928846</v>
       </c>
       <c r="N91">
-        <v>-24.4596366</v>
+        <v>-24.858846</v>
       </c>
       <c r="O91">
-        <v>-2.44596366</v>
+        <v>-2.4858846</v>
       </c>
       <c r="P91">
-        <v>-22.01367294</v>
+        <v>-22.3729614</v>
       </c>
       <c r="Q91">
-        <v>-13.08367294</v>
+        <v>-13.4429614</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3003423181362513</v>
+        <v>0.3257965499498765</v>
       </c>
       <c r="T91">
-        <v>3.937688707409913</v>
+        <v>4.331457578150905</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03115708760162213</v>
+        <v>0.03081089773938189</v>
       </c>
       <c r="W91">
-        <v>0.2284531587435375</v>
+        <v>0.2285347903130538</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3115708760162214</v>
+        <v>0.3081089773938189</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.238260966276736</v>
+        <v>0.2401609662767361</v>
       </c>
       <c r="C92">
-        <v>-120.4164309854791</v>
+        <v>-122.4164938541808</v>
       </c>
       <c r="D92">
-        <v>31.80956901452091</v>
+        <v>31.50250614581922</v>
       </c>
       <c r="E92">
-        <v>100.47</v>
+        <v>102.163</v>
       </c>
       <c r="F92">
-        <v>152.37</v>
+        <v>154.063</v>
       </c>
       <c r="G92">
         <v>0.144</v>
@@ -8825,37 +8825,37 @@
         <v>11.07</v>
       </c>
       <c r="M92">
-        <v>35.928846</v>
+        <v>36.3280554</v>
       </c>
       <c r="N92">
-        <v>-24.858846</v>
+        <v>-25.2580554</v>
       </c>
       <c r="O92">
-        <v>-2.4858846</v>
+        <v>-2.52580554</v>
       </c>
       <c r="P92">
-        <v>-22.3729614</v>
+        <v>-22.73224986</v>
       </c>
       <c r="Q92">
-        <v>-13.4429614</v>
+        <v>-13.80224986</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3257965499498765</v>
+        <v>0.356907277722085</v>
       </c>
       <c r="T92">
-        <v>4.331457578150905</v>
+        <v>4.812730642389895</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03081089773938189</v>
+        <v>0.03047231644554253</v>
       </c>
       <c r="W92">
-        <v>0.2285347903130538</v>
+        <v>0.2286146277821411</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3081089773938189</v>
+        <v>0.3047231644554252</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2401609662767361</v>
+        <v>0.242060966276736</v>
       </c>
       <c r="C93">
-        <v>-122.4164938541808</v>
+        <v>-124.4106851479504</v>
       </c>
       <c r="D93">
-        <v>31.50250614581922</v>
+        <v>31.20131485204966</v>
       </c>
       <c r="E93">
-        <v>102.163</v>
+        <v>103.856</v>
       </c>
       <c r="F93">
-        <v>154.063</v>
+        <v>155.756</v>
       </c>
       <c r="G93">
         <v>0.144</v>
@@ -8907,37 +8907,37 @@
         <v>11.07</v>
       </c>
       <c r="M93">
-        <v>36.3280554</v>
+        <v>36.72726480000001</v>
       </c>
       <c r="N93">
-        <v>-25.2580554</v>
+        <v>-25.65726480000001</v>
       </c>
       <c r="O93">
-        <v>-2.52580554</v>
+        <v>-2.565726480000001</v>
       </c>
       <c r="P93">
-        <v>-22.73224986</v>
+        <v>-23.09153832000001</v>
       </c>
       <c r="Q93">
-        <v>-13.80224986</v>
+        <v>-14.16153832000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.356907277722085</v>
+        <v>0.3957956874373457</v>
       </c>
       <c r="T93">
-        <v>4.812730642389895</v>
+        <v>5.414321972688633</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03047231644554253</v>
+        <v>0.03014109561461271</v>
       </c>
       <c r="W93">
-        <v>0.2286146277821411</v>
+        <v>0.2286927296540743</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3047231644554252</v>
+        <v>0.3014109561461271</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.242060966276736</v>
+        <v>0.243960966276736</v>
       </c>
       <c r="C94">
-        <v>-124.4106851479504</v>
+        <v>-126.3991716839247</v>
       </c>
       <c r="D94">
-        <v>31.20131485204966</v>
+        <v>30.90582831607534</v>
       </c>
       <c r="E94">
-        <v>103.856</v>
+        <v>105.549</v>
       </c>
       <c r="F94">
-        <v>155.756</v>
+        <v>157.449</v>
       </c>
       <c r="G94">
         <v>0.144</v>
@@ -8989,37 +8989,37 @@
         <v>11.07</v>
       </c>
       <c r="M94">
-        <v>36.72726480000001</v>
+        <v>37.1264742</v>
       </c>
       <c r="N94">
-        <v>-25.65726480000001</v>
+        <v>-26.0564742</v>
       </c>
       <c r="O94">
-        <v>-2.565726480000001</v>
+        <v>-2.60564742</v>
       </c>
       <c r="P94">
-        <v>-23.09153832000001</v>
+        <v>-23.45082678</v>
       </c>
       <c r="Q94">
-        <v>-14.16153832000001</v>
+        <v>-14.52082678</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3957956874373457</v>
+        <v>0.4457950713569665</v>
       </c>
       <c r="T94">
-        <v>5.414321972688633</v>
+        <v>6.18779654021558</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03014109561461271</v>
+        <v>0.02981699781230505</v>
       </c>
       <c r="W94">
-        <v>0.2286927296540743</v>
+        <v>0.2287691519158585</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3014109561461271</v>
+        <v>0.2981699781230505</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.243960966276736</v>
+        <v>0.245860966276736</v>
       </c>
       <c r="C95">
-        <v>-126.3991716839247</v>
+        <v>-128.3821140192758</v>
       </c>
       <c r="D95">
-        <v>30.90582831607534</v>
+        <v>30.6158859807242</v>
       </c>
       <c r="E95">
-        <v>105.549</v>
+        <v>107.242</v>
       </c>
       <c r="F95">
-        <v>157.449</v>
+        <v>159.142</v>
       </c>
       <c r="G95">
         <v>0.144</v>
@@ -9071,37 +9071,37 @@
         <v>11.07</v>
       </c>
       <c r="M95">
-        <v>37.1264742</v>
+        <v>37.52568360000001</v>
       </c>
       <c r="N95">
-        <v>-26.0564742</v>
+        <v>-26.45568360000001</v>
       </c>
       <c r="O95">
-        <v>-2.60564742</v>
+        <v>-2.645568360000001</v>
       </c>
       <c r="P95">
-        <v>-23.45082678</v>
+        <v>-23.81011524000001</v>
       </c>
       <c r="Q95">
-        <v>-14.52082678</v>
+        <v>-14.88011524000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4457950713569665</v>
+        <v>0.5124609165831278</v>
       </c>
       <c r="T95">
-        <v>6.18779654021558</v>
+        <v>7.219095963584846</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02981699781230505</v>
+        <v>0.02949979570791883</v>
       </c>
       <c r="W95">
-        <v>0.2287691519158585</v>
+        <v>0.2288439481720727</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2981699781230505</v>
+        <v>0.2949979570791882</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.245860966276736</v>
+        <v>0.247760966276736</v>
       </c>
       <c r="C96">
-        <v>-128.3821140192758</v>
+        <v>-130.3596667421203</v>
       </c>
       <c r="D96">
-        <v>30.6158859807242</v>
+        <v>30.33133325787972</v>
       </c>
       <c r="E96">
-        <v>107.242</v>
+        <v>108.935</v>
       </c>
       <c r="F96">
-        <v>159.142</v>
+        <v>160.835</v>
       </c>
       <c r="G96">
         <v>0.144</v>
@@ -9153,37 +9153,37 @@
         <v>11.07</v>
       </c>
       <c r="M96">
-        <v>37.52568360000001</v>
+        <v>37.924893</v>
       </c>
       <c r="N96">
-        <v>-26.45568360000001</v>
+        <v>-26.854893</v>
       </c>
       <c r="O96">
-        <v>-2.645568360000001</v>
+        <v>-2.6854893</v>
       </c>
       <c r="P96">
-        <v>-23.81011524000001</v>
+        <v>-24.1694037</v>
       </c>
       <c r="Q96">
-        <v>-14.88011524000001</v>
+        <v>-15.2394037</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5124609165831278</v>
+        <v>0.6057930998997535</v>
       </c>
       <c r="T96">
-        <v>7.219095963584846</v>
+        <v>8.662915156301819</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02949979570791883</v>
+        <v>0.02918927154257232</v>
       </c>
       <c r="W96">
-        <v>0.2288439481720727</v>
+        <v>0.2289171697702614</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2949979570791882</v>
+        <v>0.2918927154257231</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.247760966276736</v>
+        <v>0.249660966276736</v>
       </c>
       <c r="C97">
-        <v>-130.3596667421203</v>
+        <v>-132.3319787463552</v>
       </c>
       <c r="D97">
-        <v>30.33133325787972</v>
+        <v>30.05202125364476</v>
       </c>
       <c r="E97">
-        <v>108.935</v>
+        <v>110.628</v>
       </c>
       <c r="F97">
-        <v>160.835</v>
+        <v>162.528</v>
       </c>
       <c r="G97">
         <v>0.144</v>
@@ -9235,37 +9235,37 @@
         <v>11.07</v>
       </c>
       <c r="M97">
-        <v>37.924893</v>
+        <v>38.32410240000001</v>
       </c>
       <c r="N97">
-        <v>-26.854893</v>
+        <v>-27.25410240000001</v>
       </c>
       <c r="O97">
-        <v>-2.6854893</v>
+        <v>-2.725410240000001</v>
       </c>
       <c r="P97">
-        <v>-24.1694037</v>
+        <v>-24.52869216000001</v>
       </c>
       <c r="Q97">
-        <v>-15.2394037</v>
+        <v>-15.59869216000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6057930998997535</v>
+        <v>0.7457913748746923</v>
       </c>
       <c r="T97">
-        <v>8.662915156301819</v>
+        <v>10.82864394537728</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02918927154257232</v>
+        <v>0.02888521663067051</v>
       </c>
       <c r="W97">
-        <v>0.2289171697702614</v>
+        <v>0.2289888659184879</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2918927154257231</v>
+        <v>0.2888521663067052</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.249660966276736</v>
+        <v>0.251560966276736</v>
       </c>
       <c r="C98">
-        <v>-132.3319787463552</v>
+        <v>-134.2991934914477</v>
       </c>
       <c r="D98">
-        <v>30.05202125364478</v>
+        <v>29.7778065085523</v>
       </c>
       <c r="E98">
-        <v>110.628</v>
+        <v>112.321</v>
       </c>
       <c r="F98">
-        <v>162.528</v>
+        <v>164.221</v>
       </c>
       <c r="G98">
         <v>0.144</v>
@@ -9317,37 +9317,37 @@
         <v>11.07</v>
       </c>
       <c r="M98">
-        <v>38.3241024</v>
+        <v>38.7233118</v>
       </c>
       <c r="N98">
-        <v>-27.2541024</v>
+        <v>-27.6533118</v>
       </c>
       <c r="O98">
-        <v>-2.72541024</v>
+        <v>-2.76533118</v>
       </c>
       <c r="P98">
-        <v>-24.52869216</v>
+        <v>-24.88798062</v>
       </c>
       <c r="Q98">
-        <v>-15.59869216</v>
+        <v>-15.95798062</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7457913748746903</v>
+        <v>0.9791218331662538</v>
       </c>
       <c r="T98">
-        <v>10.82864394537725</v>
+        <v>14.43819192716967</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02888521663067052</v>
+        <v>0.02858743089221</v>
       </c>
       <c r="W98">
-        <v>0.2289888659184879</v>
+        <v>0.2290590837956169</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2888521663067052</v>
+        <v>0.2858743089221</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.251560966276736</v>
+        <v>0.253460966276736</v>
       </c>
       <c r="C99">
-        <v>-134.2991934914477</v>
+        <v>-136.2614492481297</v>
       </c>
       <c r="D99">
-        <v>29.7778065085523</v>
+        <v>29.50855075187033</v>
       </c>
       <c r="E99">
-        <v>112.321</v>
+        <v>114.014</v>
       </c>
       <c r="F99">
-        <v>164.221</v>
+        <v>165.914</v>
       </c>
       <c r="G99">
         <v>0.144</v>
@@ -9399,37 +9399,37 @@
         <v>11.07</v>
       </c>
       <c r="M99">
-        <v>38.7233118</v>
+        <v>39.12252120000001</v>
       </c>
       <c r="N99">
-        <v>-27.6533118</v>
+        <v>-28.05252120000001</v>
       </c>
       <c r="O99">
-        <v>-2.76533118</v>
+        <v>-2.805252120000001</v>
       </c>
       <c r="P99">
-        <v>-24.88798062</v>
+        <v>-25.24726908000001</v>
       </c>
       <c r="Q99">
-        <v>-15.95798062</v>
+        <v>-16.31726908000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9791218331662538</v>
+        <v>1.445782749749381</v>
       </c>
       <c r="T99">
-        <v>14.43819192716967</v>
+        <v>21.6572878907545</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02858743089221</v>
+        <v>0.02829572241371806</v>
       </c>
       <c r="W99">
-        <v>0.2290590837956169</v>
+        <v>0.2291278686548453</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2858743089221</v>
+        <v>0.2829572241371806</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.253460966276736</v>
+        <v>0.255360966276736</v>
       </c>
       <c r="C100">
-        <v>-136.2614492481297</v>
+        <v>-138.2188793308827</v>
       </c>
       <c r="D100">
-        <v>29.50855075187033</v>
+        <v>29.24412066911726</v>
       </c>
       <c r="E100">
-        <v>114.014</v>
+        <v>115.707</v>
       </c>
       <c r="F100">
-        <v>165.914</v>
+        <v>167.607</v>
       </c>
       <c r="G100">
         <v>0.144</v>
@@ -9481,37 +9481,37 @@
         <v>11.07</v>
       </c>
       <c r="M100">
-        <v>39.12252120000001</v>
+        <v>39.5217306</v>
       </c>
       <c r="N100">
-        <v>-28.05252120000001</v>
+        <v>-28.4517306</v>
       </c>
       <c r="O100">
-        <v>-2.805252120000001</v>
+        <v>-2.84517306</v>
       </c>
       <c r="P100">
-        <v>-25.24726908000001</v>
+        <v>-25.60655754</v>
       </c>
       <c r="Q100">
-        <v>-16.31726908000001</v>
+        <v>-16.67655754</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.445782749749381</v>
+        <v>2.845765499498761</v>
       </c>
       <c r="T100">
-        <v>21.6572878907545</v>
+        <v>43.314575781509</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02829572241371806</v>
+        <v>0.02800990703580172</v>
       </c>
       <c r="W100">
-        <v>0.2291278686548453</v>
+        <v>0.229195263920958</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2829572241371806</v>
+        <v>0.2800990703580172</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.255360966276736</v>
-      </c>
-      <c r="C101">
-        <v>-138.2188793308827</v>
-      </c>
-      <c r="D101">
-        <v>29.24412066911726</v>
-      </c>
-      <c r="E101">
-        <v>115.707</v>
-      </c>
-      <c r="F101">
-        <v>167.607</v>
-      </c>
-      <c r="G101">
-        <v>0.144</v>
-      </c>
-      <c r="H101">
-        <v>117.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>20</v>
-      </c>
-      <c r="K101">
-        <v>8.93</v>
-      </c>
-      <c r="L101">
-        <v>11.07</v>
-      </c>
-      <c r="M101">
-        <v>39.5217306</v>
-      </c>
-      <c r="N101">
-        <v>-28.4517306</v>
-      </c>
-      <c r="O101">
-        <v>-2.84517306</v>
-      </c>
-      <c r="P101">
-        <v>-25.60655754</v>
-      </c>
-      <c r="Q101">
-        <v>-16.67655754</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.845765499498761</v>
-      </c>
-      <c r="T101">
-        <v>43.314575781509</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02800990703580172</v>
-      </c>
-      <c r="W101">
-        <v>0.229195263920958</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2800990703580172</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
